--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1157,12 +1157,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1147,22 +1147,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -2329,22 +2329,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2526,22 +2526,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3127,12 +3127,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G14" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI14"/>
+  <dimension ref="A1:AU14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,245 +498,175 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Cantos_H</t>
+          <t>status</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Cantos_A</t>
+          <t>Odd_H_FT</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>status</t>
+          <t>Odd_D_FT</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_FT</t>
+          <t>Odd_A_FT</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_FT</t>
+          <t>Odd_H_HT</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_FT</t>
+          <t>Odd_D_HT</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_HT</t>
+          <t>HT_Odd_Over05</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Odd_D_HT</t>
+          <t>HT_Odd_Under05</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_HT</t>
+          <t>HT_Odd_Over15</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over05</t>
+          <t>HT_Odd_Under15</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under05</t>
+          <t>HT_Odd_Under25</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over15</t>
+          <t>FT_Odd_Over05</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under15</t>
+          <t>Odd_Over15</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Over25</t>
+          <t>Odd_Under15</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>HT_Odd_Under25</t>
+          <t>Odd_Over25</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>FT_Odd_Over05</t>
+          <t>Odd_Under25</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over15</t>
+          <t>Odd_Over35</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under15</t>
+          <t>Odd_Under35</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over25</t>
+          <t>Odd_Under45</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under25</t>
+          <t>Odd_BTTS_Yes</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over35</t>
+          <t>Odd_BTTS_No</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under35</t>
+          <t>MinGolsH</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Over45</t>
+          <t>MinGolsA</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>Odd_Under45</t>
+          <t>Odd_H_D</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_Yes</t>
+          <t>Odd_A_D</t>
         </is>
       </c>
       <c r="AL1" s="1" t="inlineStr">
         <is>
-          <t>Odd_BTTS_No</t>
+          <t>Odd_H_A</t>
         </is>
       </c>
       <c r="AM1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_D</t>
+          <t>ChutegolH</t>
         </is>
       </c>
       <c r="AN1" s="1" t="inlineStr">
         <is>
-          <t>Odd_A_D</t>
+          <t>ChutegolA</t>
         </is>
       </c>
       <c r="AO1" s="1" t="inlineStr">
         <is>
-          <t>Odd_H_A</t>
+          <t>ChuteTotalH</t>
         </is>
       </c>
       <c r="AP1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_75</t>
+          <t>ChuteTotalA</t>
         </is>
       </c>
       <c r="AQ1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_85</t>
+          <t>XGHome</t>
         </is>
       </c>
       <c r="AR1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_95</t>
+          <t>XGAway</t>
         </is>
       </c>
       <c r="AS1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_105</t>
+          <t>AtaquePerigosoH</t>
         </is>
       </c>
       <c r="AT1" s="1" t="inlineStr">
         <is>
-          <t>odds_corners_over_115</t>
+          <t>AtaquePerigosoA</t>
         </is>
       </c>
       <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_75</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_85</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_95</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_105</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_under_115</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_1</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>odds_corners_2</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_over05</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_over15</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_under05</t>
-        </is>
-      </c>
-      <c r="BE1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_under15</t>
-        </is>
-      </c>
-      <c r="BF1" s="1" t="inlineStr">
-        <is>
-          <t>odds_2nd_half_under25</t>
-        </is>
-      </c>
-      <c r="BG1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_H</t>
-        </is>
-      </c>
-      <c r="BH1" s="1" t="inlineStr">
-        <is>
-          <t>Odd_marcar_prim_A</t>
-        </is>
-      </c>
-      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>DateTime</t>
         </is>
@@ -789,16 +719,16 @@
       <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="M2" t="n">
-        <v>-1</v>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -854,11 +784,15 @@
       <c r="AG2" t="n">
         <v>0</v>
       </c>
-      <c r="AH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>0</v>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -870,16 +804,16 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -893,49 +827,7 @@
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI2" s="3" t="n">
+      <c r="AU2" s="3" t="n">
         <v>46170.29166666666</v>
       </c>
     </row>
@@ -986,16 +878,16 @@
       <c r="L3" t="n">
         <v>0</v>
       </c>
-      <c r="M3" t="n">
-        <v>-1</v>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -1051,11 +943,15 @@
       <c r="AG3" t="n">
         <v>0</v>
       </c>
-      <c r="AH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0</v>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -1067,16 +963,16 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -1090,49 +986,7 @@
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI3" s="3" t="n">
+      <c r="AU3" s="3" t="n">
         <v>46170.33333333334</v>
       </c>
     </row>
@@ -1147,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1183,16 +1037,16 @@
       <c r="L4" t="n">
         <v>0</v>
       </c>
-      <c r="M4" t="n">
-        <v>-1</v>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
@@ -1248,11 +1102,15 @@
       <c r="AG4" t="n">
         <v>0</v>
       </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0</v>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
@@ -1264,16 +1122,16 @@
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
@@ -1287,49 +1145,7 @@
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI4" s="3" t="n">
+      <c r="AU4" s="3" t="n">
         <v>46170.375</v>
       </c>
     </row>
@@ -1344,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1380,16 +1196,16 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="n">
-        <v>-1</v>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -1445,11 +1261,15 @@
       <c r="AG5" t="n">
         <v>0</v>
       </c>
-      <c r="AH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0</v>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
@@ -1461,16 +1281,16 @@
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ5" t="n">
         <v>0</v>
@@ -1484,49 +1304,7 @@
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH5" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI5" s="3" t="n">
+      <c r="AU5" s="3" t="n">
         <v>46170.375</v>
       </c>
     </row>
@@ -1577,16 +1355,16 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="n">
-        <v>-1</v>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1642,11 +1420,15 @@
       <c r="AG6" t="n">
         <v>0</v>
       </c>
-      <c r="AH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0</v>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
@@ -1658,16 +1440,16 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
@@ -1681,49 +1463,7 @@
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH6" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI6" s="3" t="n">
+      <c r="AU6" s="3" t="n">
         <v>46170.375</v>
       </c>
     </row>
@@ -1774,16 +1514,16 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
-        <v>-1</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -1839,11 +1579,15 @@
       <c r="AG7" t="n">
         <v>0</v>
       </c>
-      <c r="AH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0</v>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -1855,16 +1599,16 @@
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -1878,49 +1622,7 @@
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI7" s="3" t="n">
+      <c r="AU7" s="3" t="n">
         <v>46170.41666666666</v>
       </c>
     </row>
@@ -1935,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1971,16 +1673,16 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="n">
-        <v>-1</v>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
@@ -2036,11 +1738,15 @@
       <c r="AG8" t="n">
         <v>0</v>
       </c>
-      <c r="AH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>0</v>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -2052,16 +1758,16 @@
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -2075,49 +1781,7 @@
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI8" s="3" t="n">
+      <c r="AU8" s="3" t="n">
         <v>46170.45833333334</v>
       </c>
     </row>
@@ -2132,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2168,16 +1832,16 @@
       <c r="L9" t="n">
         <v>0</v>
       </c>
-      <c r="M9" t="n">
-        <v>-1</v>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -2233,11 +1897,15 @@
       <c r="AG9" t="n">
         <v>0</v>
       </c>
-      <c r="AH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0</v>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
@@ -2249,16 +1917,16 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ9" t="n">
         <v>0</v>
@@ -2272,49 +1940,7 @@
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI9" s="3" t="n">
+      <c r="AU9" s="3" t="n">
         <v>46170.45833333334</v>
       </c>
     </row>
@@ -2365,16 +1991,16 @@
       <c r="L10" t="n">
         <v>0</v>
       </c>
-      <c r="M10" t="n">
-        <v>-1</v>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N10" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
@@ -2430,11 +2056,15 @@
       <c r="AG10" t="n">
         <v>0</v>
       </c>
-      <c r="AH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
@@ -2446,16 +2076,16 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
@@ -2469,49 +2099,7 @@
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI10" s="3" t="n">
+      <c r="AU10" s="3" t="n">
         <v>46170.5</v>
       </c>
     </row>
@@ -2562,16 +2150,16 @@
       <c r="L11" t="n">
         <v>0</v>
       </c>
-      <c r="M11" t="n">
-        <v>-1</v>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -2627,11 +2215,15 @@
       <c r="AG11" t="n">
         <v>0</v>
       </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
@@ -2643,16 +2235,16 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -2666,49 +2258,7 @@
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI11" s="3" t="n">
+      <c r="AU11" s="3" t="n">
         <v>46170.5</v>
       </c>
     </row>
@@ -2759,16 +2309,16 @@
       <c r="L12" t="n">
         <v>0</v>
       </c>
-      <c r="M12" t="n">
-        <v>-1</v>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
@@ -2824,11 +2374,15 @@
       <c r="AG12" t="n">
         <v>0</v>
       </c>
-      <c r="AH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>0</v>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
@@ -2840,16 +2394,16 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -2863,49 +2417,7 @@
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH12" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI12" s="3" t="n">
+      <c r="AU12" s="3" t="n">
         <v>46170.54166666666</v>
       </c>
     </row>
@@ -2930,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2956,16 +2468,16 @@
       <c r="L13" t="n">
         <v>0</v>
       </c>
-      <c r="M13" t="n">
-        <v>-1</v>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -3021,11 +2533,15 @@
       <c r="AG13" t="n">
         <v>0</v>
       </c>
-      <c r="AH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -3037,16 +2553,16 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
@@ -3060,49 +2576,7 @@
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI13" s="3" t="n">
+      <c r="AU13" s="3" t="n">
         <v>46170.58333333334</v>
       </c>
     </row>
@@ -3127,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3153,16 +2627,16 @@
       <c r="L14" t="n">
         <v>0</v>
       </c>
-      <c r="M14" t="n">
-        <v>-1</v>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
       </c>
       <c r="N14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -3218,11 +2692,15 @@
       <c r="AG14" t="n">
         <v>0</v>
       </c>
-      <c r="AH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>0</v>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
@@ -3234,16 +2712,16 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
@@ -3257,49 +2735,7 @@
       <c r="AT14" t="n">
         <v>0</v>
       </c>
-      <c r="AU14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI14" s="3" t="n">
+      <c r="AU14" s="3" t="n">
         <v>46170.58333333334</v>
       </c>
     </row>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1329,12 +1329,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1319,22 +1319,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G6" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1001,22 +1001,22 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1314,27 +1314,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1464,7 +1464,7 @@
         <v>0</v>
       </c>
       <c r="AU6" s="3" t="n">
-        <v>46170.375</v>
+        <v>46170.41666666666</v>
       </c>
     </row>
     <row r="7">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1623,7 +1623,7 @@
         <v>0</v>
       </c>
       <c r="AU7" s="3" t="n">
-        <v>46170.41666666666</v>
+        <v>46170.45833333334</v>
       </c>
     </row>
     <row r="8">
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="P13" t="n">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="Q13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,13 +2633,13 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P14" t="n">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -734,55 +734,55 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -893,55 +893,55 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,13 +1520,13 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,13 +1679,13 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -725,37 +725,37 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.75</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="S2" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="U2" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="V2" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
         <v>1.3</v>
@@ -764,25 +764,25 @@
         <v>2.97</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,65 +884,65 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="R3" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="S3" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="T3" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="U3" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="V3" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.9</v>
+        <v>2.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.11</v>
+        <v>2.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.6</v>
+        <v>3.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.23</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF3" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AG3" t="n">
         <v>1.87</v>
       </c>
-      <c r="AG3" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AH3" t="inlineStr">
         <is>
           <t>[]</t>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>3.41</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>4.45</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1688,55 +1688,55 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,13 +1838,13 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.66</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.93</v>
+        <v>1.83</v>
       </c>
       <c r="S7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AK7" t="n">
         <v>1.47</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.02</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.73</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1688,55 +1688,55 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.9</v>
+        <v>2.66</v>
       </c>
       <c r="R8" t="n">
-        <v>2.86</v>
+        <v>1.93</v>
       </c>
       <c r="S8" t="n">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="T8" t="n">
-        <v>4.6</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
-        <v>1.62</v>
+        <v>3.38</v>
       </c>
       <c r="V8" t="n">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.5</v>
+        <v>2.59</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.13</v>
+        <v>2.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.37</v>
+        <v>4.45</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.66</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.29</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="O14" t="n">
-        <v>2.55</v>
+        <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.85</v>
+        <v>2.68</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>5.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1688,55 +1688,55 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V8" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD8" t="n">
         <v>2.66</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.85</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.69</v>
+        <v>2.7</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,55 +1847,55 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.9</v>
+        <v>2.66</v>
       </c>
       <c r="R9" t="n">
-        <v>2.86</v>
+        <v>1.93</v>
       </c>
       <c r="S9" t="n">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="T9" t="n">
-        <v>4.6</v>
+        <v>2.41</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>3.38</v>
       </c>
       <c r="V9" t="n">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="W9" t="n">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="Z9" t="n">
-        <v>8.5</v>
+        <v>2.59</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.13</v>
+        <v>2.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>4.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.37</v>
+        <v>4.45</v>
       </c>
       <c r="AD9" t="n">
-        <v>2.66</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.85</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1688,55 +1688,55 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.9</v>
+        <v>2.66</v>
       </c>
       <c r="R8" t="n">
-        <v>2.86</v>
+        <v>1.93</v>
       </c>
       <c r="S8" t="n">
-        <v>1.13</v>
+        <v>1.47</v>
       </c>
       <c r="T8" t="n">
-        <v>4.6</v>
+        <v>2.41</v>
       </c>
       <c r="U8" t="n">
-        <v>1.62</v>
+        <v>3.38</v>
       </c>
       <c r="V8" t="n">
-        <v>2.16</v>
+        <v>1.25</v>
       </c>
       <c r="W8" t="n">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.03</v>
+        <v>1.39</v>
       </c>
       <c r="Z8" t="n">
-        <v>8.5</v>
+        <v>2.59</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.13</v>
+        <v>2.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.6</v>
+        <v>1.56</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.37</v>
+        <v>4.45</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.66</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.85</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.4</v>
+        <v>2.02</v>
       </c>
       <c r="AG8" t="n">
-        <v>2.7</v>
+        <v>1.69</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1847,55 +1847,55 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="T9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AD9" t="n">
         <v>2.66</v>
       </c>
-      <c r="R9" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.41</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.38</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>4.45</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.14</v>
-      </c>
       <c r="AE9" t="n">
-        <v>1.02</v>
+        <v>1.85</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.02</v>
+        <v>1.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.69</v>
+        <v>2.7</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.08</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="O2" t="n">
         <v>3.31</v>
       </c>
       <c r="P2" t="n">
-        <v>3.07</v>
+        <v>2.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="R2" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="T2" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="U2" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="V2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W2" t="n">
         <v>1.02</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.97</v>
+        <v>3.04</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.7</v>
+        <v>3.58</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="AE2" t="n">
         <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.3</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -923,10 +923,10 @@
         <v>2.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="AC3" t="n">
         <v>3.72</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>2.27</v>
+        <v>3.33</v>
       </c>
       <c r="O6" t="n">
-        <v>3.41</v>
+        <v>4.27</v>
       </c>
       <c r="P6" t="n">
-        <v>3.01</v>
+        <v>1.88</v>
       </c>
       <c r="Q6" t="n">
         <v>3.24</v>
       </c>
       <c r="R6" t="n">
-        <v>1.85</v>
+        <v>2.46</v>
       </c>
       <c r="S6" t="n">
-        <v>1.58</v>
+        <v>1.22</v>
       </c>
       <c r="T6" t="n">
-        <v>2.23</v>
+        <v>3.64</v>
       </c>
       <c r="U6" t="n">
-        <v>4</v>
+        <v>2.38</v>
       </c>
       <c r="V6" t="n">
-        <v>1.19</v>
+        <v>1.48</v>
       </c>
       <c r="W6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="X6" t="n">
         <v>1.02</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y6" t="n">
-        <v>1.68</v>
+        <v>1.73</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.13</v>
+        <v>1.99</v>
       </c>
       <c r="AA6" t="n">
         <v>3.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.35</v>
+        <v>2.17</v>
       </c>
       <c r="AC6" t="n">
-        <v>6.3</v>
+        <v>2.62</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.07</v>
+        <v>1.38</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.02</v>
+        <v>1.11</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.4</v>
+        <v>1.59</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.51</v>
+        <v>2.19</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.59</v>
+        <v>1.27</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1688,55 +1688,55 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.66</v>
+        <v>5.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.93</v>
+        <v>2.86</v>
       </c>
       <c r="S8" t="n">
-        <v>1.47</v>
+        <v>1.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.41</v>
+        <v>5.8</v>
       </c>
       <c r="U8" t="n">
-        <v>3.38</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="n">
-        <v>1.25</v>
+        <v>2.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.39</v>
+        <v>1.01</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.59</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.38</v>
+        <v>1.13</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.56</v>
+        <v>4.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.45</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>2.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.02</v>
+        <v>1.66</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.02</v>
+        <v>1.33</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.69</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.73</v>
+        <v>1.09</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>7.9</v>
+        <v>2.65</v>
       </c>
       <c r="R9" t="n">
-        <v>2.86</v>
+        <v>1.95</v>
       </c>
       <c r="S9" t="n">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="T9" t="n">
-        <v>4.6</v>
+        <v>2.47</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>2.16</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
-        <v>1.34</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.4</v>
+        <v>1.97</v>
       </c>
       <c r="AG9" t="n">
-        <v>2.7</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.08</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG7" t="n">
         <v>3</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.77</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.4</v>
+        <v>3.22</v>
       </c>
       <c r="R8" t="n">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="S8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.1</v>
       </c>
-      <c r="T8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="AE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.62</v>
       </c>
-      <c r="V8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.8</v>
+        <v>2.37</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
-        <v>2.85</v>
+        <v>3.2</v>
       </c>
       <c r="Q13" t="n">
         <v>3.1</v>
@@ -2495,7 +2495,7 @@
         <v>2.18</v>
       </c>
       <c r="U13" t="n">
-        <v>3.78</v>
+        <v>4.1</v>
       </c>
       <c r="V13" t="n">
         <v>1.19</v>
@@ -2519,7 +2519,7 @@
         <v>1.38</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.35</v>
+        <v>5.86</v>
       </c>
       <c r="AD13" t="n">
         <v>1.09</v>
@@ -2633,22 +2633,22 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="O14" t="n">
         <v>2.6</v>
       </c>
       <c r="P14" t="n">
-        <v>2.68</v>
+        <v>2.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.7</v>
+        <v>3.88</v>
       </c>
       <c r="R14" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="S14" t="n">
-        <v>1.69</v>
+        <v>1.62</v>
       </c>
       <c r="T14" t="n">
         <v>2.04</v>
@@ -2663,25 +2663,25 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y14" t="n">
         <v>1.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="AA14" t="n">
         <v>2.88</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AC14" t="n">
         <v>5.35</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU14"/>
+  <dimension ref="A1:AU16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,10 +923,10 @@
         <v>2.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="AC3" t="n">
         <v>3.72</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1361,19 +1361,19 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.33</v>
+        <v>3.28</v>
       </c>
       <c r="O6" t="n">
-        <v>4.27</v>
+        <v>4.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.24</v>
+        <v>3.54</v>
       </c>
       <c r="R6" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="S6" t="n">
         <v>1.22</v>
@@ -1382,43 +1382,43 @@
         <v>3.64</v>
       </c>
       <c r="U6" t="n">
-        <v>2.38</v>
+        <v>2.48</v>
       </c>
       <c r="V6" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="W6" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.73</v>
+        <v>1.17</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.99</v>
+        <v>3.96</v>
       </c>
       <c r="AA6" t="n">
-        <v>3.2</v>
+        <v>1.68</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.17</v>
+        <v>2.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.62</v>
+        <v>2.83</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1559,7 +1559,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="AB7" t="n">
         <v>4.2</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.22</v>
+        <v>2.65</v>
       </c>
       <c r="R8" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="T8" t="n">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="U8" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.33</v>
+        <v>2.69</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.77</v>
+        <v>2.29</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.39</v>
+        <v>1.6</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.43</v>
+        <v>4.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
         <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.47</v>
+        <v>1.73</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="R9" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="S9" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="T9" t="n">
-        <v>2.47</v>
+        <v>2.27</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.29</v>
+        <v>2.77</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.39</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.25</v>
+        <v>5.43</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
         <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.73</v>
+        <v>1.47</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2039,7 +2039,7 @@
         <v>1.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AC10" t="n">
         <v>3.28</v>
@@ -2268,27 +2268,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>46170.54166666666</v>
+        <v>46170.52083333334</v>
       </c>
     </row>
     <row r="13">
@@ -2427,27 +2427,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.19</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.86</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46170.58333333334</v>
+        <v>46170.54166666666</v>
       </c>
     </row>
     <row r="14">
@@ -2737,6 +2737,324 @@
       </c>
       <c r="AU14" s="3" t="n">
         <v>46170.58333333334</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>El Geish</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Wadi Degla</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="P15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R15" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="U15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" s="3" t="n">
+        <v>46170.58333333334</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Poland 1. Liga</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Wieczysta Kraków</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Polonia Warszawa</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="3" t="n">
+        <v>46170.64583333334</v>
       </c>
     </row>
   </sheetData>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.4</v>
+        <v>2.65</v>
       </c>
       <c r="R7" t="n">
-        <v>2.86</v>
+        <v>1.95</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>5.8</v>
+        <v>2.47</v>
       </c>
       <c r="U7" t="n">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="V7" t="n">
-        <v>2.15</v>
+        <v>1.27</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AF7" t="n">
-        <v>1.33</v>
+        <v>1.97</v>
       </c>
       <c r="AG7" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.09</v>
+        <v>1.73</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.65</v>
+        <v>5.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.95</v>
+        <v>2.86</v>
       </c>
       <c r="S8" t="n">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.47</v>
+        <v>5.8</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>2.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.69</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.29</v>
+        <v>1.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.25</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.97</v>
+        <v>1.33</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.73</v>
+        <v>1.09</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,52 +2633,52 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.9</v>
+        <v>2.37</v>
       </c>
       <c r="O14" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="P14" t="n">
-        <v>2.62</v>
+        <v>3.2</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.88</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>1.71</v>
+        <v>1.82</v>
       </c>
       <c r="S14" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="T14" t="n">
-        <v>2.04</v>
+        <v>2.18</v>
       </c>
       <c r="U14" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="V14" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W14" t="n">
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.88</v>
+        <v>2.95</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.35</v>
+        <v>1.38</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.35</v>
+        <v>5.86</v>
       </c>
       <c r="AD14" t="n">
         <v>1.09</v>
@@ -2687,7 +2687,7 @@
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.21</v>
+        <v>2.15</v>
       </c>
       <c r="AG14" t="n">
         <v>1.58</v>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.32</v>
+        <v>1.49</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,52 +2792,52 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.37</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P15" t="n">
         <v>2.62</v>
       </c>
-      <c r="P15" t="n">
-        <v>3.2</v>
-      </c>
       <c r="Q15" t="n">
-        <v>3.1</v>
+        <v>3.88</v>
       </c>
       <c r="R15" t="n">
-        <v>1.82</v>
+        <v>1.71</v>
       </c>
       <c r="S15" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="T15" t="n">
-        <v>2.18</v>
+        <v>2.04</v>
       </c>
       <c r="U15" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="V15" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W15" t="n">
         <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.23</v>
+        <v>2.19</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.86</v>
+        <v>5.35</v>
       </c>
       <c r="AD15" t="n">
         <v>1.09</v>
@@ -2846,7 +2846,7 @@
         <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.15</v>
+        <v>2.21</v>
       </c>
       <c r="AG15" t="n">
         <v>1.58</v>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AK15" t="n">
         <v>1.32</v>
-      </c>
-      <c r="AK15" t="n">
-        <v>1.49</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -734,7 +734,7 @@
         <v>2.94</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="R2" t="n">
         <v>2.01</v>
@@ -767,7 +767,7 @@
         <v>2.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="AC2" t="n">
         <v>3.58</v>
@@ -779,10 +779,10 @@
         <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -923,7 +923,7 @@
         <v>2.97</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.09</v>
+        <v>2.15</v>
       </c>
       <c r="AB3" t="n">
         <v>1.71</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>1.68</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AC6" t="n">
         <v>2.83</v>
@@ -1559,10 +1559,10 @@
         <v>2.69</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
         <v>4.25</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.4</v>
+        <v>3.22</v>
       </c>
       <c r="R8" t="n">
-        <v>2.86</v>
+        <v>1.75</v>
       </c>
       <c r="S8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.43</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.1</v>
       </c>
-      <c r="T8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="U8" t="n">
+      <c r="AE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.62</v>
       </c>
-      <c r="V8" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>1.36</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.09</v>
+        <v>1.47</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.22</v>
+        <v>5.4</v>
       </c>
       <c r="R9" t="n">
-        <v>1.75</v>
+        <v>3.2</v>
       </c>
       <c r="S9" t="n">
-        <v>1.59</v>
+        <v>1.1</v>
       </c>
       <c r="T9" t="n">
-        <v>2.27</v>
+        <v>5.8</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>2.15</v>
       </c>
       <c r="W9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.01</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.08</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.33</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.77</v>
+        <v>1.18</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.39</v>
+        <v>4.2</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.43</v>
+        <v>1.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.14</v>
+        <v>1.33</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.62</v>
+        <v>3</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.36</v>
+        <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.47</v>
+        <v>1.09</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="O10" t="n">
         <v>3.17</v>
       </c>
       <c r="P10" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="R10" t="n">
         <v>1.98</v>
       </c>
       <c r="S10" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.56</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
         <v>2.82</v>
@@ -2039,7 +2039,7 @@
         <v>1.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
         <v>3.28</v>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.03</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="P7" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.65</v>
+        <v>3.22</v>
       </c>
       <c r="R7" t="n">
-        <v>1.95</v>
+        <v>1.75</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="T7" t="n">
-        <v>2.47</v>
+        <v>2.27</v>
       </c>
       <c r="U7" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.53</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.69</v>
+        <v>2.33</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.38</v>
+        <v>2.77</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.57</v>
+        <v>1.39</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.25</v>
+        <v>5.43</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.97</v>
+        <v>2.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.68</v>
+        <v>1.47</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>2.03</v>
       </c>
       <c r="O8" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.22</v>
+        <v>2.65</v>
       </c>
       <c r="R8" t="n">
-        <v>1.75</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="T8" t="n">
-        <v>2.27</v>
+        <v>2.47</v>
       </c>
       <c r="U8" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.02</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.33</v>
+        <v>2.69</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.77</v>
+        <v>2.38</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.39</v>
+        <v>1.57</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.43</v>
+        <v>4.25</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.1</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
         <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.14</v>
+        <v>1.97</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.62</v>
+        <v>1.73</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.47</v>
+        <v>1.68</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.22</v>
+        <v>3.14</v>
       </c>
       <c r="R7" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="S7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
         <v>3.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.53</v>
+        <v>1.46</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.33</v>
+        <v>2.44</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.43</v>
+        <v>5.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.14</v>
+        <v>2.07</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -2315,13 +2315,13 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.03</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -2354,10 +2354,10 @@
         <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.37</v>
+        <v>2.29</v>
       </c>
       <c r="O14" t="n">
         <v>2.62</v>
       </c>
       <c r="P14" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Q14" t="n">
         <v>3.2</v>
       </c>
-      <c r="Q14" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R14" t="n">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="T14" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="U14" t="n">
-        <v>4.1</v>
+        <v>3.58</v>
       </c>
       <c r="V14" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="W14" t="n">
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.23</v>
+        <v>2.34</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.95</v>
+        <v>2.82</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.86</v>
+        <v>5.52</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="O15" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
         <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="R15" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="S15" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="T15" t="n">
-        <v>2.04</v>
+        <v>2.11</v>
       </c>
       <c r="U15" t="n">
-        <v>3.85</v>
+        <v>3.58</v>
       </c>
       <c r="V15" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
         <v>1.01</v>
       </c>
       <c r="X15" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.11</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>5.35</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.09</v>
       </c>
       <c r="AE15" t="n">
         <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.21</v>
+        <v>2.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.14</v>
+        <v>2.65</v>
       </c>
       <c r="R7" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="U7" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.02</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.65</v>
+        <v>5.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.45</v>
+        <v>1.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.47</v>
+        <v>5.8</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>2.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.69</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.38</v>
+        <v>1.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.57</v>
+        <v>4.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.25</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>2.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.97</v>
+        <v>1.33</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.68</v>
+        <v>1.09</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.4</v>
+        <v>3.14</v>
       </c>
       <c r="R9" t="n">
-        <v>3.2</v>
+        <v>1.78</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="T9" t="n">
-        <v>5.8</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>2.15</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.35</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AK9" t="n">
-        <v>1.09</v>
+        <v>1.48</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,25 +2633,25 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.29</v>
+        <v>2.85</v>
       </c>
       <c r="O14" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P14" t="n">
         <v>2.62</v>
       </c>
-      <c r="P14" t="n">
-        <v>3.35</v>
-      </c>
       <c r="Q14" t="n">
-        <v>3.2</v>
+        <v>3.78</v>
       </c>
       <c r="R14" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="T14" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="U14" t="n">
         <v>3.58</v>
@@ -2663,34 +2663,34 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.82</v>
+        <v>2.55</v>
       </c>
       <c r="AB14" t="n">
         <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.52</v>
+        <v>4.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE14" t="n">
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.85</v>
+        <v>2.29</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>2.62</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>3.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.78</v>
+        <v>3.2</v>
       </c>
       <c r="R15" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="S15" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="T15" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="U15" t="n">
         <v>3.58</v>
@@ -2822,34 +2822,34 @@
         <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.55</v>
+        <v>2.82</v>
       </c>
       <c r="AB15" t="n">
         <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.9</v>
+        <v>5.52</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AE15" t="n">
         <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="R7" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="S7" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="T7" t="n">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V7" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.35</v>
+        <v>2.03</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>3.3</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.14</v>
+        <v>2.65</v>
       </c>
       <c r="R9" t="n">
-        <v>1.78</v>
+        <v>1.95</v>
       </c>
       <c r="S9" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="T9" t="n">
-        <v>2.18</v>
+        <v>2.47</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
         <v>1.02</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y9" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.44</v>
+        <v>2.69</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.64</v>
+        <v>2.38</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.25</v>
+        <v>4.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
         <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.07</v>
+        <v>1.97</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.66</v>
+        <v>1.73</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.35</v>
+        <v>1.27</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.48</v>
+        <v>1.68</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.44</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="O2" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="P2" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="Q2" t="n">
         <v>2.88</v>
@@ -740,10 +740,10 @@
         <v>2.01</v>
       </c>
       <c r="S2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="T2" t="n">
-        <v>2.66</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
         <v>2.96</v>
@@ -767,7 +767,7 @@
         <v>2.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AC2" t="n">
         <v>3.58</v>
@@ -779,10 +779,10 @@
         <v>1.03</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -884,16 +884,16 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="O3" t="n">
         <v>3.37</v>
       </c>
       <c r="P3" t="n">
-        <v>3.19</v>
+        <v>3.17</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="R3" t="n">
         <v>2.02</v>
@@ -917,22 +917,22 @@
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.97</v>
+        <v>2.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.15</v>
+        <v>2.09</v>
       </c>
       <c r="AB3" t="n">
         <v>1.71</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.72</v>
+        <v>3.74</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
         <v>1.02</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="O6" t="n">
-        <v>4.33</v>
+        <v>4.17</v>
       </c>
       <c r="P6" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="R6" t="n">
-        <v>2.49</v>
+        <v>2.43</v>
       </c>
       <c r="S6" t="n">
-        <v>1.22</v>
+        <v>1.29</v>
       </c>
       <c r="T6" t="n">
-        <v>3.64</v>
+        <v>3.25</v>
       </c>
       <c r="U6" t="n">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="V6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="W6" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="X6" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.96</v>
+        <v>4.1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.06</v>
+        <v>2.09</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG7" t="n">
         <v>3</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.4</v>
+        <v>2.78</v>
       </c>
       <c r="R8" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="U8" t="n">
         <v>3.2</v>
       </c>
-      <c r="S8" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="T8" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.62</v>
-      </c>
       <c r="V8" t="n">
-        <v>2.15</v>
+        <v>1.27</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AF8" t="n">
-        <v>1.33</v>
+        <v>1.92</v>
       </c>
       <c r="AG8" t="n">
-        <v>3</v>
+        <v>1.77</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.09</v>
+        <v>1.65</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.03</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.65</v>
+        <v>3.14</v>
       </c>
       <c r="R9" t="n">
-        <v>1.95</v>
+        <v>1.78</v>
       </c>
       <c r="S9" t="n">
-        <v>1.45</v>
+        <v>1.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.47</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.46</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.69</v>
+        <v>2.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.38</v>
+        <v>2.64</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.57</v>
+        <v>1.43</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.25</v>
+        <v>5.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
         <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.97</v>
+        <v>2.07</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.68</v>
+        <v>1.48</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2156,16 +2156,16 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
         <v>3.17</v>
       </c>
       <c r="P11" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="R11" t="n">
         <v>1.98</v>
@@ -2226,7 +2226,7 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
         <v>1.51</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,80 +1520,80 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.4</v>
+        <v>3.14</v>
       </c>
       <c r="R7" t="n">
-        <v>3.2</v>
+        <v>1.78</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="T7" t="n">
-        <v>5.8</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="V7" t="n">
-        <v>2.15</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ7" t="n">
         <v>1.35</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.13</v>
-      </c>
       <c r="AK7" t="n">
-        <v>1.09</v>
+        <v>1.48</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,65 +1838,65 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG9" t="n">
         <v>3</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.48</v>
+        <v>1.09</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2633,7 +2633,7 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.85</v>
+        <v>2.75</v>
       </c>
       <c r="O14" t="n">
         <v>2.7</v>
@@ -2642,13 +2642,13 @@
         <v>2.62</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="R14" t="n">
         <v>1.75</v>
       </c>
       <c r="S14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="T14" t="n">
         <v>2.11</v>
@@ -2663,7 +2663,7 @@
         <v>1.01</v>
       </c>
       <c r="X14" t="n">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="Y14" t="n">
         <v>1.54</v>
@@ -2672,7 +2672,7 @@
         <v>2.32</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.55</v>
+        <v>2.63</v>
       </c>
       <c r="AB14" t="n">
         <v>1.4</v>
@@ -2792,55 +2792,55 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="O15" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="P15" t="n">
-        <v>3.35</v>
+        <v>3.1</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.2</v>
+        <v>3.04</v>
       </c>
       <c r="R15" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="S15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="T15" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="U15" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X15" t="n">
         <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.82</v>
+        <v>2.51</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.52</v>
+        <v>5.1</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE15" t="n">
         <v>1.03</v>
@@ -2849,7 +2849,7 @@
         <v>2.05</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -923,7 +923,7 @@
         <v>2.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.09</v>
+        <v>2.06</v>
       </c>
       <c r="AB3" t="n">
         <v>1.71</v>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1403,7 +1403,7 @@
         <v>1.66</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.09</v>
+        <v>2.12</v>
       </c>
       <c r="AC6" t="n">
         <v>2.7</v>
@@ -1700,13 +1700,13 @@
         <v>2.5</v>
       </c>
       <c r="U8" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="V8" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="X8" t="n">
         <v>1.02</v>
@@ -1865,10 +1865,10 @@
         <v>2.15</v>
       </c>
       <c r="W9" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
         <v>1.01</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="O12" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="P12" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="n">
         <v>1.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,52 +2633,52 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.75</v>
+        <v>2.28</v>
       </c>
       <c r="O14" t="n">
-        <v>2.7</v>
+        <v>2.65</v>
       </c>
       <c r="P14" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.76</v>
+        <v>3.04</v>
       </c>
       <c r="R14" t="n">
-        <v>1.75</v>
+        <v>1.86</v>
       </c>
       <c r="S14" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="T14" t="n">
-        <v>2.11</v>
+        <v>2.26</v>
       </c>
       <c r="U14" t="n">
-        <v>3.58</v>
+        <v>3.5</v>
       </c>
       <c r="V14" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W14" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.54</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.32</v>
+        <v>2.28</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.63</v>
+        <v>2.51</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AD14" t="n">
         <v>1.11</v>
@@ -2687,10 +2687,10 @@
         <v>1.03</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,52 +2792,52 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.28</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>2.65</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.04</v>
+        <v>3.76</v>
       </c>
       <c r="R15" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="S15" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="T15" t="n">
-        <v>2.26</v>
+        <v>2.11</v>
       </c>
       <c r="U15" t="n">
-        <v>3.5</v>
+        <v>3.58</v>
       </c>
       <c r="V15" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.51</v>
+        <v>2.63</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AD15" t="n">
         <v>1.11</v>
@@ -2846,10 +2846,10 @@
         <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.05</v>
+        <v>2.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2960,55 +2960,55 @@
         <v>3.98</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.31</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.78</v>
+        <v>5.4</v>
       </c>
       <c r="R8" t="n">
-        <v>1.97</v>
+        <v>3.2</v>
       </c>
       <c r="S8" t="n">
-        <v>1.44</v>
+        <v>1.1</v>
       </c>
       <c r="T8" t="n">
-        <v>2.5</v>
+        <v>5.8</v>
       </c>
       <c r="U8" t="n">
-        <v>3.25</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>2.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.05</v>
+        <v>1.34</v>
       </c>
       <c r="X8" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.36</v>
+        <v>1.01</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.7</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.3</v>
+        <v>1.18</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.16</v>
+        <v>2.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.92</v>
+        <v>1.33</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.77</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.3</v>
+        <v>1.13</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.65</v>
+        <v>1.09</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>3.31</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.4</v>
+        <v>2.78</v>
       </c>
       <c r="R9" t="n">
-        <v>3.2</v>
+        <v>1.97</v>
       </c>
       <c r="S9" t="n">
-        <v>1.1</v>
+        <v>1.44</v>
       </c>
       <c r="T9" t="n">
-        <v>5.8</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>1.62</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>2.15</v>
+        <v>1.3</v>
       </c>
       <c r="W9" t="n">
-        <v>1.34</v>
+        <v>1.05</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.01</v>
       </c>
-      <c r="Z9" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AF9" t="n">
-        <v>1.33</v>
+        <v>1.92</v>
       </c>
       <c r="AG9" t="n">
-        <v>3</v>
+        <v>1.77</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.13</v>
+        <v>1.3</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.09</v>
+        <v>1.65</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.82</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -725,64 +725,64 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
       <c r="O2" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="P2" t="n">
-        <v>2.93</v>
+        <v>2.85</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>2.01</v>
+        <v>1.97</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>2.53</v>
       </c>
       <c r="U2" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="V2" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.04</v>
+        <v>2.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.06</v>
+        <v>2.19</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.73</v>
+        <v>1.64</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.58</v>
+        <v>3.96</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.21</v>
+        <v>2.13</v>
       </c>
       <c r="O3" t="n">
-        <v>3.37</v>
+        <v>3.27</v>
       </c>
       <c r="P3" t="n">
-        <v>3.17</v>
+        <v>3.44</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="R3" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="S3" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="T3" t="n">
-        <v>2.66</v>
+        <v>2.44</v>
       </c>
       <c r="U3" t="n">
-        <v>3.02</v>
+        <v>3.32</v>
       </c>
       <c r="V3" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="W3" t="n">
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.92</v>
+        <v>2.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.06</v>
+        <v>2.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.71</v>
+        <v>1.58</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.74</v>
+        <v>4.4</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="AE3" t="n">
         <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.82</v>
+        <v>1.9</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1361,77 +1361,77 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.42</v>
+        <v>3.56</v>
       </c>
       <c r="O6" t="n">
-        <v>4.17</v>
+        <v>2.96</v>
       </c>
       <c r="P6" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="S6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="U6" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>3.92</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AF6" t="n">
         <v>1.87</v>
       </c>
-      <c r="Q6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="R6" t="n">
-        <v>2.43</v>
-      </c>
-      <c r="S6" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T6" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="U6" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AD6" t="n">
+      <c r="AG6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.36</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.2</v>
       </c>
       <c r="AK6" t="n">
         <v>1.29</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>3.77</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.14</v>
+        <v>2.57</v>
       </c>
       <c r="R7" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB7" t="n">
         <v>1.6</v>
       </c>
-      <c r="T7" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AC7" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE7" t="n">
         <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1679,19 +1679,19 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q8" t="n">
         <v>5.4</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2</v>
+        <v>2.86</v>
       </c>
       <c r="S8" t="n">
         <v>1.1</v>
@@ -1706,7 +1706,7 @@
         <v>2.15</v>
       </c>
       <c r="W8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>
@@ -1730,7 +1730,7 @@
         <v>2.4</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.66</v>
+        <v>1.82</v>
       </c>
       <c r="AF8" t="n">
         <v>1.33</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.16</v>
+        <v>2.33</v>
       </c>
       <c r="O9" t="n">
-        <v>3.31</v>
+        <v>2.75</v>
       </c>
       <c r="P9" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.78</v>
+        <v>3.14</v>
       </c>
       <c r="R9" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="S9" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.36</v>
+        <v>1.51</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.7</v>
+        <v>2.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.3</v>
+        <v>2.64</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
         <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.92</v>
+        <v>2.07</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.77</v>
+        <v>1.66</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.3</v>
+        <v>1.35</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="O10" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="P10" t="n">
-        <v>2.93</v>
+        <v>3.07</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.02</v>
+        <v>2.88</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>2.82</v>
+        <v>2.91</v>
       </c>
       <c r="V10" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X10" t="n">
         <v>1.02</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.05</v>
+        <v>2.97</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.96</v>
+        <v>2.07</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.28</v>
+        <v>3.42</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.51</v>
+        <v>1.56</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AU16"/>
+  <dimension ref="A1:AU17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1043,13 +1043,13 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -1082,10 +1082,10 @@
         <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
@@ -1202,13 +1202,13 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -1241,10 +1241,10 @@
         <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.57</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.34</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.78</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.33</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.33</v>
+        <v>1.97</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>3.42</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>3.77</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.14</v>
+        <v>2.57</v>
       </c>
       <c r="R9" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="S9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U9" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB9" t="n">
         <v>1.6</v>
       </c>
-      <c r="T9" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.43</v>
-      </c>
       <c r="AC9" t="n">
-        <v>5.25</v>
+        <v>4.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
         <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.07</v>
+        <v>1.93</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1950,27 +1950,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="O10" t="n">
-        <v>3.23</v>
+        <v>2.8</v>
       </c>
       <c r="P10" t="n">
-        <v>3.07</v>
+        <v>3</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.88</v>
+        <v>3.14</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="T10" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>2.91</v>
+        <v>3.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.33</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>1.06</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.3</v>
+        <v>1.51</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.97</v>
+        <v>2.44</v>
       </c>
       <c r="AA10" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF10" t="n">
         <v>2.07</v>
       </c>
-      <c r="AB10" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.42</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="AG10" t="n">
-        <v>1.91</v>
+        <v>1.66</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
         <v>0</v>
       </c>
       <c r="AU10" s="3" t="n">
-        <v>46170.5</v>
+        <v>46170.45833333334</v>
       </c>
     </row>
     <row r="11">
@@ -2268,27 +2268,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.05</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="P12" t="n">
-        <v>2.18</v>
+        <v>3.07</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.4</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>2.62</v>
+        <v>2.91</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.05</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.11</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.67</v>
+        <v>1.78</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.05</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.36</v>
+        <v>1.56</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>46170.52083333334</v>
+        <v>46170.5</v>
       </c>
     </row>
     <row r="13">
@@ -2427,27 +2427,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.82</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46170.54166666666</v>
+        <v>46170.52083333334</v>
       </c>
     </row>
     <row r="14">
@@ -2586,27 +2586,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.04</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.26</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.51</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>46170.58333333334</v>
+        <v>46170.54166666666</v>
       </c>
     </row>
     <row r="15">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.76</v>
+        <v>3.06</v>
       </c>
       <c r="R15" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="S15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="T15" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="U15" t="n">
         <v>3.58</v>
@@ -2822,34 +2822,34 @@
         <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.63</v>
+        <v>2.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE15" t="n">
         <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2904,156 +2904,315 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Egypt Egyptian Premier League</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Ismaily SC</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pharco</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="O16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>3.76</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="U16" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="3" t="n">
+        <v>46170.58333333334</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>15:30</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Poland 1. Liga</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
+      <c r="D17" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>Wieczysta Kraków</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>Polonia Warszawa</t>
         </is>
       </c>
-      <c r="G16" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" t="inlineStr">
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="N16" t="n">
+      <c r="N17" t="n">
         <v>1.69</v>
       </c>
-      <c r="O16" t="n">
+      <c r="O17" t="n">
         <v>3.9</v>
       </c>
-      <c r="P16" t="n">
+      <c r="P17" t="n">
         <v>3.98</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="Q17" t="n">
         <v>2.23</v>
       </c>
-      <c r="R16" t="n">
+      <c r="R17" t="n">
         <v>2.43</v>
       </c>
-      <c r="S16" t="n">
+      <c r="S17" t="n">
         <v>1.28</v>
       </c>
-      <c r="T16" t="n">
+      <c r="T17" t="n">
         <v>3.18</v>
       </c>
-      <c r="U16" t="n">
+      <c r="U17" t="n">
         <v>2.29</v>
       </c>
-      <c r="V16" t="n">
+      <c r="V17" t="n">
         <v>1.52</v>
       </c>
-      <c r="W16" t="n">
+      <c r="W17" t="n">
         <v>1.12</v>
       </c>
-      <c r="X16" t="n">
+      <c r="X17" t="n">
         <v>1.03</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="Y17" t="n">
         <v>1.18</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="Z17" t="n">
         <v>4.4</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AA17" t="n">
         <v>1.62</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AB17" t="n">
         <v>2.15</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AC17" t="n">
         <v>2.46</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AD17" t="n">
         <v>1.44</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AE17" t="n">
         <v>1.19</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AF17" t="n">
         <v>1.54</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AG17" t="n">
         <v>2.25</v>
       </c>
-      <c r="AH16" t="inlineStr">
+      <c r="AH17" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI16" t="inlineStr">
+      <c r="AI17" t="inlineStr">
         <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AJ17" t="n">
         <v>1.29</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AK17" t="n">
         <v>1.83</v>
       </c>
-      <c r="AL16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU16" s="3" t="n">
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>-1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" s="3" t="n">
         <v>46170.64583333334</v>
       </c>
     </row>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.86</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.18</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,65 +1997,65 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>3.71</v>
       </c>
       <c r="O10" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="P10" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG10" t="n">
         <v>3</v>
       </c>
-      <c r="Q10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.49</v>
+        <v>1.09</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2474,13 +2474,13 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="O13" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q13" t="n">
         <v>3.4</v>
@@ -2489,49 +2489,49 @@
         <v>2.2</v>
       </c>
       <c r="S13" t="n">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="T13" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="U13" t="n">
         <v>2.62</v>
       </c>
       <c r="V13" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="W13" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="X13" t="n">
         <v>1.05</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.85</v>
+        <v>1.91</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AD13" t="n">
         <v>1.3</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AG13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2547,7 +2547,7 @@
         <v>1.33</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.06</v>
+        <v>3.76</v>
       </c>
       <c r="R15" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="S15" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="T15" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="U15" t="n">
         <v>3.58</v>
@@ -2822,34 +2822,34 @@
         <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE15" t="n">
         <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,25 +2951,25 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="O16" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="P16" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.76</v>
+        <v>3.06</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="S16" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="T16" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="U16" t="n">
         <v>3.58</v>
@@ -2981,34 +2981,34 @@
         <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE16" t="n">
         <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3110,16 +3110,16 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.69</v>
+        <v>1.82</v>
       </c>
       <c r="O17" t="n">
-        <v>3.9</v>
+        <v>3.54</v>
       </c>
       <c r="P17" t="n">
-        <v>3.98</v>
+        <v>3.74</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="R17" t="n">
         <v>2.43</v>
@@ -3155,19 +3155,19 @@
         <v>2.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.46</v>
+        <v>2.51</v>
       </c>
       <c r="AD17" t="n">
         <v>1.44</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.83</v>
+        <v>1.91</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,65 +1520,65 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>3.71</v>
       </c>
       <c r="O7" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="P7" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="R7" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V7" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AG7" t="n">
         <v>3</v>
       </c>
-      <c r="Q7" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="R7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.44</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.13</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.49</v>
+        <v>1.09</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="O9" t="n">
-        <v>3.42</v>
+        <v>2.8</v>
       </c>
       <c r="P9" t="n">
-        <v>3.77</v>
+        <v>3</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.57</v>
+        <v>3.14</v>
       </c>
       <c r="R9" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="S9" t="n">
-        <v>1.42</v>
+        <v>1.55</v>
       </c>
       <c r="T9" t="n">
-        <v>2.56</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
-        <v>2.95</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.34</v>
+        <v>1.51</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.78</v>
+        <v>2.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.6</v>
+        <v>1.43</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.33</v>
+        <v>5.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="AE9" t="n">
         <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.93</v>
+        <v>2.07</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.76</v>
+        <v>1.66</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.29</v>
+        <v>1.35</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.78</v>
+        <v>1.49</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.71</v>
+        <v>1.97</v>
       </c>
       <c r="O10" t="n">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="P10" t="n">
-        <v>1.96</v>
+        <v>3.77</v>
       </c>
       <c r="Q10" t="n">
-        <v>5.4</v>
+        <v>2.57</v>
       </c>
       <c r="R10" t="n">
-        <v>2.86</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1</v>
+        <v>1.42</v>
       </c>
       <c r="T10" t="n">
-        <v>5.8</v>
+        <v>2.56</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>2.95</v>
       </c>
       <c r="V10" t="n">
-        <v>2.15</v>
+        <v>1.28</v>
       </c>
       <c r="W10" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.01</v>
       </c>
-      <c r="Z10" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.82</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.33</v>
+        <v>1.93</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>1.76</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.13</v>
+        <v>1.29</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.09</v>
+        <v>1.78</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.07</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="O15" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="P15" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.76</v>
+        <v>3.06</v>
       </c>
       <c r="R15" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="S15" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="T15" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="U15" t="n">
         <v>3.58</v>
@@ -2822,34 +2822,34 @@
         <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE15" t="n">
         <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,25 +2951,25 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="O16" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="P16" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.06</v>
+        <v>3.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="S16" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="T16" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="U16" t="n">
         <v>3.58</v>
@@ -2981,34 +2981,34 @@
         <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE16" t="n">
         <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -725,13 +725,13 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="O2" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.85</v>
+        <v>2.82</v>
       </c>
       <c r="Q2" t="n">
         <v>3.1</v>
@@ -764,13 +764,13 @@
         <v>2.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.96</v>
+        <v>4</v>
       </c>
       <c r="AD2" t="n">
         <v>1.17</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
       <c r="O3" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>3.44</v>
+        <v>3.45</v>
       </c>
       <c r="Q3" t="n">
         <v>2.77</v>
@@ -938,10 +938,10 @@
         <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.9</v>
+        <v>1.98</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="O6" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2.24</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="R6" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="S6" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T6" t="n">
-        <v>2.33</v>
+        <v>2.47</v>
       </c>
       <c r="U6" t="n">
-        <v>3.18</v>
+        <v>3.15</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
@@ -1391,22 +1391,22 @@
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.74</v>
+        <v>2.83</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.19</v>
+        <v>2.16</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.92</v>
+        <v>3.9</v>
       </c>
       <c r="AD6" t="n">
         <v>1.18</v>
@@ -1415,10 +1415,10 @@
         <v>1.02</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.36</v>
+        <v>1.32</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1520,19 +1520,19 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.71</v>
+        <v>3.54</v>
       </c>
       <c r="O7" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="P7" t="n">
-        <v>1.96</v>
+        <v>1.87</v>
       </c>
       <c r="Q7" t="n">
-        <v>5.4</v>
+        <v>7.9</v>
       </c>
       <c r="R7" t="n">
-        <v>2.86</v>
+        <v>3.2</v>
       </c>
       <c r="S7" t="n">
         <v>1.1</v>
@@ -1553,25 +1553,25 @@
         <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Z7" t="n">
-        <v>9.800000000000001</v>
+        <v>7.9</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.18</v>
+        <v>1.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>4.2</v>
+        <v>1.79</v>
       </c>
       <c r="AC7" t="n">
         <v>1.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.4</v>
+        <v>2.66</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.82</v>
+        <v>1.66</v>
       </c>
       <c r="AF7" t="n">
         <v>1.33</v>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.13</v>
+        <v>1.27</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.09</v>
+        <v>1.25</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1997,16 +1997,16 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="O10" t="n">
-        <v>3.42</v>
+        <v>3.25</v>
       </c>
       <c r="P10" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="R10" t="n">
         <v>2</v>
@@ -2018,7 +2018,7 @@
         <v>2.56</v>
       </c>
       <c r="U10" t="n">
-        <v>2.95</v>
+        <v>3.18</v>
       </c>
       <c r="V10" t="n">
         <v>1.28</v>
@@ -2027,7 +2027,7 @@
         <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
         <v>1.34</v>
@@ -2039,7 +2039,7 @@
         <v>2.2</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AC10" t="n">
         <v>4.33</v>
@@ -2051,10 +2051,10 @@
         <v>1.01</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.07</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.97</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.74</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.42</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.61</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="P4" t="n">
-        <v>2.66</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>4.51</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.75</v>
+        <v>2.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.33</v>
+        <v>2.58</v>
       </c>
       <c r="O5" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="P5" t="n">
-        <v>2.23</v>
+        <v>2.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,25 +2792,25 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.33</v>
+        <v>2.75</v>
       </c>
       <c r="O15" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="P15" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.06</v>
+        <v>3.76</v>
       </c>
       <c r="R15" t="n">
-        <v>1.85</v>
+        <v>1.9</v>
       </c>
       <c r="S15" t="n">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="T15" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="U15" t="n">
         <v>3.58</v>
@@ -2822,34 +2822,34 @@
         <v>1.01</v>
       </c>
       <c r="X15" t="n">
-        <v>1.07</v>
+        <v>1.11</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.95</v>
+        <v>4.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.13</v>
+        <v>1.11</v>
       </c>
       <c r="AE15" t="n">
         <v>1.03</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -2919,12 +2919,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,25 +2951,25 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.75</v>
+        <v>2.33</v>
       </c>
       <c r="O16" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="P16" t="n">
-        <v>2.62</v>
+        <v>3.05</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.76</v>
+        <v>3.06</v>
       </c>
       <c r="R16" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="S16" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="T16" t="n">
-        <v>2.11</v>
+        <v>2.24</v>
       </c>
       <c r="U16" t="n">
         <v>3.58</v>
@@ -2981,34 +2981,34 @@
         <v>1.01</v>
       </c>
       <c r="X16" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="Z16" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="AB16" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="AE16" t="n">
         <v>1.03</v>
       </c>
       <c r="AF16" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AK16" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="O4" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>2.72</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.51</v>
+        <v>3.42</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="T4" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="U4" t="n">
-        <v>4.1</v>
+        <v>3.68</v>
       </c>
       <c r="V4" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD4" t="n">
         <v>1.09</v>
       </c>
-      <c r="Y4" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AE4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.32</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="O5" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="P5" t="n">
-        <v>2.72</v>
+        <v>2.22</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.42</v>
+        <v>4.51</v>
       </c>
       <c r="R5" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="S5" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="U5" t="n">
-        <v>3.68</v>
+        <v>4.1</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.32</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.54</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="P8" t="n">
-        <v>1.87</v>
+        <v>2.62</v>
       </c>
       <c r="Q8" t="n">
-        <v>7.9</v>
+        <v>3.8</v>
       </c>
       <c r="R8" t="n">
-        <v>3.2</v>
+        <v>1.74</v>
       </c>
       <c r="S8" t="n">
-        <v>1.1</v>
+        <v>1.65</v>
       </c>
       <c r="T8" t="n">
-        <v>5.8</v>
+        <v>2.1</v>
       </c>
       <c r="U8" t="n">
-        <v>1.62</v>
+        <v>3.68</v>
       </c>
       <c r="V8" t="n">
-        <v>2.15</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
-        <v>1.35</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.02</v>
+        <v>1.5</v>
       </c>
       <c r="Z8" t="n">
-        <v>7.9</v>
+        <v>2.29</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.98</v>
+        <v>2.63</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.79</v>
+        <v>1.39</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.5</v>
+        <v>5.48</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.66</v>
+        <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.66</v>
+        <v>1.03</v>
       </c>
       <c r="AF8" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AK8" t="n">
         <v>1.33</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>3</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>1.25</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="R9" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="S9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="T9" t="n">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="U9" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="V9" t="n">
         <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
         <v>1.07</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.44</v>
+        <v>2.39</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.25</v>
+        <v>5</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.07</v>
+        <v>2.11</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.92</v>
+        <v>3.54</v>
       </c>
       <c r="O10" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.8</v>
+        <v>1.87</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.56</v>
+        <v>7.9</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>3.2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.42</v>
+        <v>1.1</v>
       </c>
       <c r="T10" t="n">
-        <v>2.56</v>
+        <v>5.8</v>
       </c>
       <c r="U10" t="n">
-        <v>3.18</v>
+        <v>1.62</v>
       </c>
       <c r="V10" t="n">
-        <v>1.28</v>
+        <v>2.15</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="X10" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.34</v>
+        <v>1.02</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.78</v>
+        <v>7.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.64</v>
+        <v>1.79</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.33</v>
+        <v>1.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.17</v>
+        <v>2.66</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.92</v>
+        <v>1.33</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.77</v>
+        <v>3</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.78</v>
+        <v>1.25</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2109,7 +2109,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,81 +2156,81 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.25</v>
+        <v>1.92</v>
       </c>
       <c r="O11" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="P11" t="n">
-        <v>2.8</v>
+        <v>3.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="R11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T11" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="V11" t="n">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="X11" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.34</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.97</v>
+        <v>2.78</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.42</v>
+        <v>4.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.23</v>
+        <v>1.17</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="AF11" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.78</v>
       </c>
-      <c r="AG11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.56</v>
-      </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>0</v>
       </c>
       <c r="AU11" s="3" t="n">
-        <v>46170.5</v>
+        <v>46170.45833333334</v>
       </c>
     </row>
     <row r="12">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2418,7 +2418,7 @@
         <v>0</v>
       </c>
       <c r="AU12" s="3" t="n">
-        <v>46170.5</v>
+        <v>46170.45833333334</v>
       </c>
     </row>
     <row r="13">
@@ -2427,12 +2427,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2442,12 +2442,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Chrobry Głogów</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.91</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>0</v>
       </c>
       <c r="AU13" s="3" t="n">
-        <v>46170.52083333334</v>
+        <v>46170.5</v>
       </c>
     </row>
     <row r="14">
@@ -2586,12 +2586,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Georgia Erovnuli Liga</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Torpedo Kutaisi</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gagra</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2736,7 +2736,7 @@
         <v>0</v>
       </c>
       <c r="AU14" s="3" t="n">
-        <v>46170.54166666666</v>
+        <v>46170.5</v>
       </c>
     </row>
     <row r="15">
@@ -2745,12 +2745,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2760,12 +2760,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Chrobry Głogów</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="R15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="S15" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="T15" t="n">
         <v>2.7</v>
       </c>
-      <c r="P15" t="n">
+      <c r="U15" t="n">
         <v>2.62</v>
       </c>
-      <c r="Q15" t="n">
-        <v>3.76</v>
-      </c>
-      <c r="R15" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S15" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="T15" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="U15" t="n">
-        <v>3.58</v>
-      </c>
       <c r="V15" t="n">
-        <v>1.21</v>
+        <v>1.41</v>
       </c>
       <c r="W15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X15" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.54</v>
+        <v>1.29</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.32</v>
+        <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.75</v>
+        <v>1.91</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.03</v>
+        <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>2.11</v>
+        <v>1.71</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.64</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="AK15" t="n">
         <v>1.33</v>
@@ -2895,7 +2895,7 @@
         <v>0</v>
       </c>
       <c r="AU15" s="3" t="n">
-        <v>46170.58333333334</v>
+        <v>46170.52083333334</v>
       </c>
     </row>
     <row r="16">
@@ -2904,27 +2904,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Georgia Erovnuli Liga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Torpedo Kutaisi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Gagra</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2951,80 +2951,80 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>3.06</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
-        <v>1.85</v>
+        <v>2.4</v>
       </c>
       <c r="S16" t="n">
-        <v>1.57</v>
+        <v>1.32</v>
       </c>
       <c r="T16" t="n">
-        <v>2.24</v>
+        <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>3.58</v>
+        <v>2.4</v>
       </c>
       <c r="V16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ16" t="n">
         <v>1.21</v>
       </c>
-      <c r="W16" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X16" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AA16" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>4.95</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AE16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF16" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.31</v>
-      </c>
       <c r="AK16" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
         <v>0</v>
       </c>
       <c r="AU16" s="3" t="n">
-        <v>46170.58333333334</v>
+        <v>46170.54166666666</v>
       </c>
     </row>
     <row r="17">

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -725,19 +725,19 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.42</v>
+        <v>2.37</v>
       </c>
       <c r="O2" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P2" t="n">
-        <v>2.82</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
         <v>3.1</v>
       </c>
       <c r="R2" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="S2" t="n">
         <v>1.43</v>
@@ -752,22 +752,22 @@
         <v>1.28</v>
       </c>
       <c r="W2" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="X2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="AC2" t="n">
         <v>4</v>
@@ -776,14 +776,14 @@
         <v>1.17</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF2" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AG2" t="n">
         <v>1.85</v>
       </c>
-      <c r="AG2" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
           <t>[]</t>
@@ -795,10 +795,10 @@
         </is>
       </c>
       <c r="AJ2" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,13 +884,13 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>3.27</v>
       </c>
       <c r="P3" t="n">
-        <v>3.45</v>
+        <v>3.44</v>
       </c>
       <c r="Q3" t="n">
         <v>2.77</v>
@@ -914,7 +914,7 @@
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="Y3" t="n">
         <v>1.38</v>
@@ -923,16 +923,16 @@
         <v>2.62</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.4</v>
+        <v>4.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="AE3" t="n">
         <v>1.02</v>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.58</v>
+        <v>3.35</v>
       </c>
       <c r="O4" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="P4" t="n">
-        <v>2.72</v>
+        <v>2.22</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.42</v>
+        <v>4.51</v>
       </c>
       <c r="R4" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="S4" t="n">
-        <v>1.55</v>
+        <v>1.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.26</v>
+        <v>2.16</v>
       </c>
       <c r="U4" t="n">
-        <v>3.68</v>
+        <v>4.1</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.34</v>
+        <v>2.17</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.59</v>
+        <v>2.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.3</v>
+        <v>7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.11</v>
+        <v>2.27</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>1.54</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.32</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.38</v>
+        <v>1.25</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.35</v>
+        <v>2.58</v>
       </c>
       <c r="O5" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="P5" t="n">
-        <v>2.22</v>
+        <v>2.72</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.51</v>
+        <v>3.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="S5" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="T5" t="n">
-        <v>2.16</v>
+        <v>2.26</v>
       </c>
       <c r="U5" t="n">
-        <v>4.1</v>
+        <v>3.68</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AD5" t="n">
         <v>1.09</v>
       </c>
-      <c r="Y5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.08</v>
-      </c>
       <c r="AE5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.27</v>
+        <v>2.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.54</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.32</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,16 +1361,16 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.2</v>
+        <v>4.45</v>
       </c>
       <c r="R6" t="n">
         <v>1.92</v>
@@ -1400,16 +1400,16 @@
         <v>2.83</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.16</v>
+        <v>2.19</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="AC6" t="n">
         <v>3.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AE6" t="n">
         <v>1.02</v>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O8" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="P8" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="Q8" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U8" t="n">
         <v>3.8</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.68</v>
-      </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.29</v>
+        <v>2.39</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.63</v>
+        <v>2.48</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.48</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
         <v>1.11</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.45</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="P9" t="n">
-        <v>3.15</v>
+        <v>2.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.04</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.86</v>
+        <v>1.74</v>
       </c>
       <c r="S9" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="T9" t="n">
-        <v>2.26</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>3.8</v>
+        <v>3.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.39</v>
+        <v>2.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.48</v>
+        <v>2.63</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>5.48</v>
       </c>
       <c r="AD9" t="n">
         <v>1.11</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="U10" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>7.9</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AG10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2159,61 +2159,61 @@
         <v>1.92</v>
       </c>
       <c r="O11" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="S11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
-        <v>2.56</v>
+        <v>2.63</v>
       </c>
       <c r="U11" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="V11" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W11" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.01</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.07</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="AC11" t="n">
         <v>4.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>1.29</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2636,22 +2636,22 @@
         <v>2.25</v>
       </c>
       <c r="O14" t="n">
-        <v>3.05</v>
+        <v>3.23</v>
       </c>
       <c r="P14" t="n">
-        <v>2.8</v>
+        <v>3.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="T14" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="U14" t="n">
         <v>3</v>
@@ -2660,37 +2660,37 @@
         <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.07</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.42</v>
+        <v>3.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="AE14" t="n">
         <v>1.07</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.78</v>
+        <v>1.85</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,7 +2703,7 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AK14" t="n">
         <v>1.56</v>
@@ -2798,7 +2798,7 @@
         <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="Q15" t="n">
         <v>3.4</v>
@@ -2807,22 +2807,22 @@
         <v>2.2</v>
       </c>
       <c r="S15" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="U15" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="V15" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="W15" t="n">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="Y15" t="n">
         <v>1.29</v>
@@ -2837,7 +2837,7 @@
         <v>1.8</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="AD15" t="n">
         <v>1.3</v>
@@ -2846,10 +2846,10 @@
         <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -3113,16 +3113,16 @@
         <v>1.82</v>
       </c>
       <c r="O17" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="R17" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="S17" t="n">
         <v>1.28</v>
@@ -3155,7 +3155,7 @@
         <v>2.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.51</v>
+        <v>2.46</v>
       </c>
       <c r="AD17" t="n">
         <v>1.44</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -746,43 +746,43 @@
         <v>2.53</v>
       </c>
       <c r="U2" t="n">
-        <v>3.15</v>
+        <v>3.12</v>
       </c>
       <c r="V2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="X2" t="n">
         <v>1.06</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.02</v>
       </c>
       <c r="Y2" t="n">
         <v>1.36</v>
       </c>
       <c r="Z2" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="AC2" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.17</v>
+        <v>1.22</v>
       </c>
       <c r="AE2" t="n">
         <v>1.02</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.32</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -884,64 +884,64 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>2.13</v>
+        <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="P3" t="n">
-        <v>3.44</v>
+        <v>3.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.77</v>
+        <v>2.66</v>
       </c>
       <c r="R3" t="n">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="S3" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="T3" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="U3" t="n">
-        <v>3.32</v>
+        <v>3.08</v>
       </c>
       <c r="V3" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="W3" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X3" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.62</v>
+        <v>2.88</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.33</v>
+        <v>3.76</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="AE3" t="n">
         <v>1.02</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -954,10 +954,10 @@
         </is>
       </c>
       <c r="AJ3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="P4" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.51</v>
+        <v>4.8</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="T4" t="n">
-        <v>2.16</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
         <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.9</v>
+        <v>3.02</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="AC4" t="n">
         <v>7</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.27</v>
+        <v>2.34</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P5" t="n">
         <v>2.58</v>
       </c>
-      <c r="O5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="P5" t="n">
-        <v>2.72</v>
-      </c>
       <c r="Q5" t="n">
-        <v>3.42</v>
+        <v>4.11</v>
       </c>
       <c r="R5" t="n">
-        <v>1.82</v>
+        <v>1.74</v>
       </c>
       <c r="S5" t="n">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="T5" t="n">
-        <v>2.26</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>3.68</v>
+        <v>3.82</v>
       </c>
       <c r="V5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
         <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.34</v>
+        <v>2.27</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.65</v>
+        <v>3.3</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.45</v>
+        <v>4.25</v>
       </c>
       <c r="R6" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="S6" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="T6" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="U6" t="n">
-        <v>3.15</v>
+        <v>3.18</v>
       </c>
       <c r="V6" t="n">
         <v>1.28</v>
@@ -1391,50 +1391,50 @@
         <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y6" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ6" t="n">
         <v>1.33</v>
       </c>
-      <c r="Z6" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.19</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AG6" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ6" t="n">
-        <v>1.32</v>
-      </c>
       <c r="AK6" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="O8" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="P8" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="Q8" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z8" t="n">
         <v>3.04</v>
       </c>
-      <c r="R8" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AA8" t="n">
-        <v>2.48</v>
+        <v>2.11</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="O9" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="P9" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="R9" t="n">
-        <v>1.74</v>
+        <v>2.25</v>
       </c>
       <c r="S9" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="U9" t="n">
-        <v>3.68</v>
+        <v>2.6</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X9" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.29</v>
+        <v>3.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.63</v>
+        <v>1.9</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.48</v>
+        <v>3.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.92</v>
+        <v>2.75</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="P11" t="n">
-        <v>3.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.58</v>
+        <v>3.8</v>
       </c>
       <c r="R11" t="n">
-        <v>1.99</v>
+        <v>1.74</v>
       </c>
       <c r="S11" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="T11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.63</v>
       </c>
-      <c r="U11" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AK11" t="n">
         <v>1.33</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>1.76</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.6</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2951,13 +2951,13 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>7.26</v>
       </c>
       <c r="Q16" t="n">
         <v>1.92</v>
@@ -2972,43 +2972,43 @@
         <v>3.1</v>
       </c>
       <c r="U16" t="n">
-        <v>2.4</v>
+        <v>2.63</v>
       </c>
       <c r="V16" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="W16" t="n">
         <v>1.11</v>
       </c>
       <c r="X16" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AB16" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="AD16" t="n">
         <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P7" t="n">
-        <v>3.21</v>
+        <v>2.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.16</v>
+        <v>3.8</v>
       </c>
       <c r="R7" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="S7" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="T7" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="U7" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="V7" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AC7" t="n">
-        <v>5</v>
+        <v>5.48</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,65 +1679,65 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.73</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.3</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.33</v>
+        <v>3.12</v>
       </c>
       <c r="R8" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="T8" t="n">
-        <v>2.56</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.01</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="AB8" t="n">
+      <c r="AF8" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AG8" t="n">
         <v>1.67</v>
       </c>
-      <c r="AC8" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
           <t>[]</t>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.01</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5.1</v>
+        <v>2.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="T9" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U9" t="n">
         <v>3.05</v>
       </c>
-      <c r="U9" t="n">
-        <v>2.6</v>
-      </c>
       <c r="V9" t="n">
-        <v>1.43</v>
+        <v>1.32</v>
       </c>
       <c r="W9" t="n">
-        <v>1.09</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.85</v>
+        <v>1.67</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.83</v>
+        <v>2.2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.19</v>
+        <v>2.3</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="O10" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>3.15</v>
+        <v>4.2</v>
       </c>
       <c r="Q10" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R10" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z10" t="n">
         <v>3.04</v>
       </c>
-      <c r="R10" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="S10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AA10" t="n">
-        <v>2.48</v>
+        <v>2.11</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>5</v>
+        <v>3.95</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.75</v>
+        <v>3.8</v>
       </c>
       <c r="O11" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.62</v>
+        <v>1.8</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.8</v>
+        <v>5.1</v>
       </c>
       <c r="R11" t="n">
-        <v>1.74</v>
+        <v>2.25</v>
       </c>
       <c r="S11" t="n">
-        <v>1.65</v>
+        <v>1.33</v>
       </c>
       <c r="T11" t="n">
-        <v>2.1</v>
+        <v>3.05</v>
       </c>
       <c r="U11" t="n">
-        <v>3.68</v>
+        <v>2.6</v>
       </c>
       <c r="V11" t="n">
-        <v>1.2</v>
+        <v>1.43</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="X11" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.29</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.63</v>
+        <v>1.9</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.39</v>
+        <v>1.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.48</v>
+        <v>3.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.12</v>
+        <v>1.83</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.63</v>
+        <v>1.92</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.33</v>
+        <v>1.19</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>3.04</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>2.55</v>
       </c>
       <c r="O4" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>2.23</v>
+        <v>2.58</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.8</v>
+        <v>4.11</v>
       </c>
       <c r="R4" t="n">
         <v>1.74</v>
       </c>
       <c r="S4" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U4" t="n">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="V4" t="n">
         <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC4" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.36</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>3.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.23</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.11</v>
+        <v>4.8</v>
       </c>
       <c r="R5" t="n">
         <v>1.74</v>
       </c>
       <c r="S5" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="V5" t="n">
         <v>1.18</v>
       </c>
       <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.02</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF5" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.74</v>
+        <v>2.15</v>
       </c>
       <c r="S7" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="T7" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="AA7" t="n">
         <v>2.1</v>
       </c>
-      <c r="U7" t="n">
-        <v>3.68</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.7</v>
-      </c>
       <c r="AB7" t="n">
-        <v>1.39</v>
+        <v>1.67</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.48</v>
+        <v>3.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.12</v>
+        <v>2.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.33</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q9" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.1</v>
       </c>
-      <c r="R9" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.56</v>
-      </c>
       <c r="U9" t="n">
-        <v>3.05</v>
+        <v>3.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.03</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF9" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O11" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U11" t="n">
         <v>3.8</v>
       </c>
-      <c r="O11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.6</v>
-      </c>
       <c r="V11" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="W11" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE11" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y11" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF11" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.45</v>
+        <v>3.8</v>
       </c>
       <c r="O12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="U12" t="n">
         <v>2.6</v>
       </c>
-      <c r="P12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.04</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U12" t="n">
-        <v>3.8</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.22</v>
+        <v>1.43</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="X12" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.52</v>
+        <v>1.29</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.39</v>
+        <v>3.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.48</v>
+        <v>1.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.42</v>
+        <v>1.85</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.5</v>
+        <v>3.4</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.11</v>
+        <v>1.3</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>1.12</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.11</v>
+        <v>1.83</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.64</v>
+        <v>1.92</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2792,7 +2792,7 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O15" t="n">
         <v>3.2</v>
@@ -2831,10 +2831,10 @@
         <v>3.3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC15" t="n">
         <v>3.29</v>
@@ -3110,13 +3110,13 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="O17" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="P17" t="n">
-        <v>3.78</v>
+        <v>3.5</v>
       </c>
       <c r="Q17" t="n">
         <v>2.2</v>
@@ -3131,10 +3131,10 @@
         <v>3.18</v>
       </c>
       <c r="U17" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="V17" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="W17" t="n">
         <v>1.12</v>
@@ -3155,7 +3155,7 @@
         <v>2.15</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="AD17" t="n">
         <v>1.44</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.55</v>
+        <v>3.55</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8</v>
+        <v>2.69</v>
       </c>
       <c r="P4" t="n">
-        <v>2.58</v>
+        <v>2.23</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.11</v>
+        <v>4.8</v>
       </c>
       <c r="R4" t="n">
         <v>1.74</v>
       </c>
       <c r="S4" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="T4" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>3.82</v>
+        <v>4.4</v>
       </c>
       <c r="V4" t="n">
         <v>1.18</v>
       </c>
       <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.02</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF4" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1116,7 +1116,7 @@
         <v>1.36</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.55</v>
+        <v>2.55</v>
       </c>
       <c r="O5" t="n">
-        <v>2.69</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>2.23</v>
+        <v>2.58</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.8</v>
+        <v>4.11</v>
       </c>
       <c r="R5" t="n">
         <v>1.74</v>
       </c>
       <c r="S5" t="n">
-        <v>1.66</v>
+        <v>1.62</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.14</v>
       </c>
       <c r="U5" t="n">
-        <v>4.4</v>
+        <v>3.82</v>
       </c>
       <c r="V5" t="n">
         <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.11</v>
+        <v>1.08</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.08</v>
+        <v>2.27</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.02</v>
+        <v>2.7</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AC5" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.51</v>
+        <v>1.59</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q7" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="T7" t="n">
         <v>2.1</v>
       </c>
-      <c r="R7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.56</v>
-      </c>
       <c r="U7" t="n">
-        <v>3.05</v>
+        <v>3.68</v>
       </c>
       <c r="V7" t="n">
-        <v>1.32</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE7" t="n">
         <v>1.03</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF7" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.37</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>3.4</v>
       </c>
       <c r="P8" t="n">
-        <v>3.25</v>
+        <v>1.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.12</v>
+        <v>5.1</v>
       </c>
       <c r="R8" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="S8" t="n">
-        <v>1.54</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>3.05</v>
       </c>
       <c r="U8" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="Z8" t="n">
         <v>3.5</v>
       </c>
-      <c r="V8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.44</v>
-      </c>
       <c r="AA8" t="n">
-        <v>2.43</v>
+        <v>1.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.85</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.12</v>
       </c>
-      <c r="AE8" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.92</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>1.19</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O9" t="n">
         <v>2.75</v>
       </c>
-      <c r="O9" t="n">
-        <v>2.65</v>
-      </c>
       <c r="P9" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>3.12</v>
       </c>
       <c r="R9" t="n">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="S9" t="n">
-        <v>1.65</v>
+        <v>1.54</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="U9" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE9" t="n">
         <v>1.01</v>
       </c>
-      <c r="X9" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>5.48</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF9" t="n">
-        <v>2.12</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.63</v>
+        <v>1.67</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S10" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
         <v>2.56</v>
       </c>
       <c r="U10" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V10" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X10" t="n">
         <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB10" t="n">
         <v>1.67</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>1.73</v>
       </c>
       <c r="O11" t="n">
-        <v>2.6</v>
+        <v>3.3</v>
       </c>
       <c r="P11" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="Q11" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z11" t="n">
         <v>3.04</v>
       </c>
-      <c r="R11" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.39</v>
-      </c>
       <c r="AA11" t="n">
-        <v>2.48</v>
+        <v>2.11</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.42</v>
+        <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.5</v>
+        <v>3.95</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>1.19</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.11</v>
+        <v>1.85</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.5</v>
+        <v>2.01</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="O12" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="P12" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="R12" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U12" t="n">
         <v>3.8</v>
       </c>
-      <c r="O12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>5.1</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="T12" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.6</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>1.09</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.04</v>
       </c>
-      <c r="Y12" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.12</v>
-      </c>
       <c r="AF12" t="n">
-        <v>1.83</v>
+        <v>2.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.92</v>
+        <v>1.64</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>3.23</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.91</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.31</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.56</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.23</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -725,40 +725,40 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="O2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P2" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Q2" t="n">
         <v>3</v>
       </c>
-      <c r="P2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>3.1</v>
-      </c>
       <c r="R2" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="S2" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="T2" t="n">
         <v>2.53</v>
       </c>
       <c r="U2" t="n">
-        <v>3.12</v>
+        <v>2.95</v>
       </c>
       <c r="V2" t="n">
         <v>1.29</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.01</v>
       </c>
       <c r="X2" t="n">
         <v>1.06</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z2" t="n">
         <v>2.83</v>
@@ -770,19 +770,19 @@
         <v>1.66</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF2" t="n">
         <v>1.83</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
@@ -798,7 +798,7 @@
         <v>1.32</v>
       </c>
       <c r="AK2" t="n">
-        <v>1.47</v>
+        <v>1.49</v>
       </c>
       <c r="AL2" t="n">
         <v>0</v>
@@ -887,61 +887,61 @@
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>3.1</v>
+        <v>3.31</v>
       </c>
       <c r="P3" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="R3" t="n">
-        <v>1.97</v>
+        <v>2.1</v>
       </c>
       <c r="S3" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T3" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U3" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W3" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
         <v>1.01</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.76</v>
+        <v>3.72</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="AE3" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>1.3</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AL3" t="n">
         <v>0</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="O6" t="n">
         <v>3.1</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="S6" t="n">
         <v>1.47</v>
       </c>
       <c r="T6" t="n">
-        <v>2.41</v>
+        <v>2.62</v>
       </c>
       <c r="U6" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="W6" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
         <v>1.03</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="AB6" t="n">
         <v>1.57</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="AD6" t="n">
         <v>1.2</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1434,7 +1434,7 @@
         <v>1.33</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="O7" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="P7" t="n">
-        <v>2.71</v>
+        <v>3.7</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="R7" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="S7" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="T7" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U7" t="n">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.48</v>
+        <v>3.86</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>3.8</v>
+        <v>2.3</v>
       </c>
       <c r="O8" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="Q8" t="n">
-        <v>5.1</v>
+        <v>3.12</v>
       </c>
       <c r="R8" t="n">
-        <v>2.25</v>
+        <v>1.95</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.54</v>
       </c>
       <c r="T8" t="n">
-        <v>3.05</v>
+        <v>2.18</v>
       </c>
       <c r="U8" t="n">
-        <v>2.6</v>
+        <v>3.5</v>
       </c>
       <c r="V8" t="n">
-        <v>1.43</v>
+        <v>1.22</v>
       </c>
       <c r="W8" t="n">
-        <v>1.09</v>
+        <v>1.02</v>
       </c>
       <c r="X8" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.5</v>
+        <v>2.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>1.9</v>
+        <v>2.43</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.12</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.83</v>
+        <v>2.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.92</v>
+        <v>1.67</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.19</v>
+        <v>1.5</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="O9" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="P9" t="n">
-        <v>3.25</v>
+        <v>2.71</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.12</v>
+        <v>3.8</v>
       </c>
       <c r="R9" t="n">
-        <v>1.95</v>
+        <v>1.74</v>
       </c>
       <c r="S9" t="n">
-        <v>1.54</v>
+        <v>1.65</v>
       </c>
       <c r="T9" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="U9" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W9" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.49</v>
+        <v>1.55</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.44</v>
+        <v>2.29</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.43</v>
+        <v>2.7</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.44</v>
+        <v>1.39</v>
       </c>
       <c r="AC9" t="n">
-        <v>5</v>
+        <v>5.48</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.05</v>
+        <v>2.12</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>3.86</v>
       </c>
       <c r="R10" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T10" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="U10" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.9</v>
+        <v>3.14</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
         <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.3</v>
+        <v>1.31</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="R11" t="n">
-        <v>2.02</v>
+        <v>2.15</v>
       </c>
       <c r="S11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T11" t="n">
         <v>2.56</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="V11" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W11" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X11" t="n">
         <v>1.06</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.04</v>
+        <v>2.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AB11" t="n">
         <v>1.67</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.75</v>
+        <v>1.6</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.01</v>
+        <v>2.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>3.06</v>
+        <v>2.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
         <v>1.4</v>
       </c>
       <c r="T14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U14" t="n">
         <v>2.75</v>
       </c>
-      <c r="U14" t="n">
-        <v>2.91</v>
-      </c>
       <c r="V14" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.31</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
         <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.85</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>1.32</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.55</v>
+        <v>2.2</v>
       </c>
       <c r="O4" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="P4" t="n">
-        <v>2.23</v>
+        <v>3.15</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="R4" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="S4" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="T4" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U4" t="n">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.65</v>
+        <v>1.53</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.02</v>
+        <v>2.62</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.31</v>
+        <v>1.38</v>
       </c>
       <c r="AC4" t="n">
-        <v>7</v>
+        <v>5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.55</v>
+        <v>3.4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="P5" t="n">
-        <v>2.58</v>
+        <v>2.25</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
         <v>1.74</v>
       </c>
       <c r="S5" t="n">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="T5" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="U5" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE5" t="n">
         <v>1.02</v>
       </c>
-      <c r="X5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF5" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1275,7 +1275,7 @@
         <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.3</v>
+        <v>1.22</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1478,22 +1478,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.83</v>
+        <v>2.75</v>
       </c>
       <c r="O7" t="n">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="P7" t="n">
-        <v>3.7</v>
+        <v>2.71</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.45</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>1.97</v>
+        <v>1.9</v>
       </c>
       <c r="S7" t="n">
-        <v>1.44</v>
+        <v>1.66</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="U7" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="V7" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="W7" t="n">
         <v>1.01</v>
       </c>
       <c r="X7" t="n">
-        <v>1.02</v>
+        <v>1.14</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.33</v>
+        <v>1.56</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.88</v>
+        <v>2.25</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.17</v>
+        <v>2.63</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.66</v>
+        <v>1.38</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.86</v>
+        <v>5.54</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.26</v>
+        <v>1.36</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.79</v>
+        <v>1.4</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.12</v>
+        <v>2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="S8" t="n">
-        <v>1.54</v>
+        <v>1.4</v>
       </c>
       <c r="T8" t="n">
-        <v>2.18</v>
+        <v>2.54</v>
       </c>
       <c r="U8" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>1.22</v>
+        <v>1.31</v>
       </c>
       <c r="W8" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="X8" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.43</v>
+        <v>2.05</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.44</v>
+        <v>1.65</v>
       </c>
       <c r="AC8" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="AF8" t="n">
         <v>2.05</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.5</v>
+        <v>2.3</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.75</v>
+        <v>1.83</v>
       </c>
       <c r="O9" t="n">
-        <v>2.65</v>
+        <v>3.15</v>
       </c>
       <c r="P9" t="n">
-        <v>2.71</v>
+        <v>3.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.8</v>
+        <v>2.45</v>
       </c>
       <c r="R9" t="n">
-        <v>1.74</v>
+        <v>1.97</v>
       </c>
       <c r="S9" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="T9" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
       <c r="U9" t="n">
-        <v>3.68</v>
+        <v>3.2</v>
       </c>
       <c r="V9" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="W9" t="n">
         <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.14</v>
+        <v>1.02</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.55</v>
+        <v>1.33</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.29</v>
+        <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.7</v>
+        <v>2.17</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.48</v>
+        <v>3.86</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.11</v>
+        <v>1.22</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.12</v>
+        <v>1.85</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.33</v>
+        <v>1.79</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -2114,7 +2114,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF11" t="n">
         <v>2.1</v>
       </c>
-      <c r="R11" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AG11" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.3</v>
+        <v>1.51</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2283,12 +2283,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O12" t="n">
-        <v>2.6</v>
+        <v>2.86</v>
       </c>
       <c r="P12" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="R12" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T12" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="U12" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="V12" t="n">
         <v>1.22</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X12" t="n">
         <v>1.07</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.39</v>
+        <v>2.45</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.5</v>
+        <v>4.65</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF12" t="n">
-        <v>2.11</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>1.69</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2951,64 +2951,64 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="O16" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="P16" t="n">
-        <v>7.26</v>
+        <v>5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.92</v>
+        <v>2.03</v>
       </c>
       <c r="R16" t="n">
-        <v>2.4</v>
+        <v>2.17</v>
       </c>
       <c r="S16" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="T16" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="U16" t="n">
-        <v>2.63</v>
+        <v>2.53</v>
       </c>
       <c r="V16" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W16" t="n">
-        <v>1.11</v>
+        <v>1.09</v>
       </c>
       <c r="X16" t="n">
         <v>1.02</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>4.2</v>
+        <v>3.82</v>
       </c>
       <c r="AA16" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AB16" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.88</v>
+        <v>2.7</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AE16" t="n">
-        <v>1.14</v>
+        <v>1.1</v>
       </c>
       <c r="AF16" t="n">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,12 +1011,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1043,64 +1043,64 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
       <c r="O4" t="n">
-        <v>2.75</v>
+        <v>2.68</v>
       </c>
       <c r="P4" t="n">
-        <v>3.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>2</v>
+        <v>1.74</v>
       </c>
       <c r="S4" t="n">
-        <v>1.58</v>
+        <v>1.66</v>
       </c>
       <c r="T4" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="U4" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.85</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AE4" t="n">
         <v>1.02</v>
       </c>
-      <c r="X4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>2.31</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF4" t="n">
-        <v>2.15</v>
+        <v>2.34</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
@@ -1113,10 +1113,10 @@
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
@@ -1170,12 +1170,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1202,64 +1202,64 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.4</v>
+        <v>2.2</v>
       </c>
       <c r="O5" t="n">
-        <v>2.68</v>
+        <v>2.75</v>
       </c>
       <c r="P5" t="n">
-        <v>2.25</v>
+        <v>3.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="R5" t="n">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="T5" t="n">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="U5" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.11</v>
+        <v>1.07</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.02</v>
+        <v>2.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.85</v>
+        <v>5.4</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.34</v>
+        <v>2.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
@@ -1272,10 +1272,10 @@
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.22</v>
+        <v>1.49</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,55 +1520,55 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.75</v>
+        <v>2.45</v>
       </c>
       <c r="O7" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="P7" t="n">
-        <v>2.71</v>
+        <v>2.94</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="S7" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="T7" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="U7" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.54</v>
+        <v>4.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="AE7" t="n">
         <v>1.03</v>
@@ -1577,7 +1577,7 @@
         <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.65</v>
+        <v>1.56</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1647,12 +1647,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,61 +1679,61 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2.71</v>
       </c>
       <c r="Q8" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
       <c r="R8" t="n">
-        <v>2.15</v>
+        <v>1.9</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.66</v>
       </c>
       <c r="T8" t="n">
-        <v>2.54</v>
+        <v>2.08</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="W8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.03</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF8" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG8" t="n">
         <v>1.65</v>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.25</v>
+        <v>1.36</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.3</v>
+        <v>1.4</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,22 +1796,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="S9" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T9" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="U9" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V9" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X9" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z9" t="n">
         <v>2.88</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1908,10 +1908,10 @@
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,22 +1955,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O10" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="Q10" t="n">
         <v>3</v>
-      </c>
-      <c r="O10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>3.86</v>
       </c>
       <c r="R10" t="n">
         <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="T10" t="n">
-        <v>2.62</v>
+        <v>2.18</v>
       </c>
       <c r="U10" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="V10" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="W10" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="X10" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.01</v>
       </c>
-      <c r="Y10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF10" t="n">
-        <v>1.71</v>
+        <v>2.05</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.95</v>
+        <v>1.67</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.31</v>
+        <v>1.51</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2114,22 +2114,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,64 +2156,64 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.45</v>
+        <v>3</v>
       </c>
       <c r="O11" t="n">
-        <v>2.66</v>
+        <v>3.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.94</v>
+        <v>2.06</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.1</v>
+        <v>3.86</v>
       </c>
       <c r="R11" t="n">
+        <v>2</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.83</v>
       </c>
-      <c r="S11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.26</v>
-      </c>
-      <c r="U11" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.42</v>
-      </c>
       <c r="AC11" t="n">
-        <v>4.9</v>
+        <v>3.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.11</v>
+        <v>1.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.56</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>1.31</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.51</v>
+        <v>1.31</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.3</v>
+        <v>1.83</v>
       </c>
       <c r="O12" t="n">
-        <v>2.86</v>
+        <v>3.15</v>
       </c>
       <c r="P12" t="n">
-        <v>3.35</v>
+        <v>3.7</v>
       </c>
       <c r="Q12" t="n">
-        <v>3</v>
+        <v>2.45</v>
       </c>
       <c r="R12" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="S12" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="T12" t="n">
-        <v>2.18</v>
+        <v>2.5</v>
       </c>
       <c r="U12" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="V12" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="AD12" t="n">
         <v>1.22</v>
       </c>
-      <c r="W12" t="n">
+      <c r="AE12" t="n">
         <v>1.02</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>4.65</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.35</v>
+        <v>1.26</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.51</v>
+        <v>1.79</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.4</v>
+        <v>1.69</v>
       </c>
       <c r="O13" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.69</v>
+        <v>2.4</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="P14" t="n">
-        <v>4.75</v>
+        <v>2.55</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,28 +2792,28 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O15" t="n">
         <v>3.2</v>
       </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.4</v>
+        <v>3.92</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2</v>
+        <v>2.25</v>
       </c>
       <c r="S15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="T15" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="U15" t="n">
         <v>2.74</v>
-      </c>
-      <c r="U15" t="n">
-        <v>2.88</v>
       </c>
       <c r="V15" t="n">
         <v>1.37</v>
@@ -2822,34 +2822,34 @@
         <v>1.07</v>
       </c>
       <c r="X15" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="n">
         <v>1.95</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.85</v>
+        <v>1.75</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.29</v>
+        <v>3.37</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="AE15" t="n">
         <v>1.1</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3110,64 +3110,64 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="P17" t="n">
-        <v>3.5</v>
+        <v>3.68</v>
       </c>
       <c r="Q17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R17" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="U17" t="n">
         <v>2.2</v>
       </c>
-      <c r="R17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="T17" t="n">
-        <v>3.18</v>
-      </c>
-      <c r="U17" t="n">
-        <v>2.27</v>
-      </c>
       <c r="V17" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="W17" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.18</v>
+        <v>1.13</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AF17" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.83</v>
+        <v>1.9</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -702,130 +702,130 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>2.35</v>
+        <v>2.6</v>
       </c>
       <c r="O2" t="n">
         <v>3.1</v>
       </c>
       <c r="P2" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="Q2" t="n">
         <v>3</v>
       </c>
       <c r="R2" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="S2" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T2" t="n">
-        <v>2.53</v>
+        <v>2.78</v>
       </c>
       <c r="U2" t="n">
-        <v>2.95</v>
+        <v>2.75</v>
       </c>
       <c r="V2" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="W2" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>['32', '90+5']</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>['35', '60']</t>
+        </is>
+      </c>
+      <c r="AJ2" t="n">
         <v>1.29</v>
       </c>
-      <c r="W2" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AD2" t="n">
+      <c r="AK2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>6</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>12</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>9</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="AR2" t="n">
         <v>1.18</v>
       </c>
-      <c r="AE2" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AG2" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ2" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AK2" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="AL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0</v>
-      </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AU2" s="3" t="n">
         <v>46170.29166666666</v>
@@ -861,130 +861,130 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N3" t="n">
         <v>2</v>
       </c>
       <c r="O3" t="n">
-        <v>3.31</v>
+        <v>3</v>
       </c>
       <c r="P3" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="R3" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="S3" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="T3" t="n">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="U3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>['27', '71', '90+2']</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>['87', '89']</t>
+        </is>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>7</v>
+      </c>
+      <c r="AN3" t="n">
         <v>3</v>
       </c>
-      <c r="V3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W3" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X3" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y3" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="Z3" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="AA3" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ3" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>-1</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>-1</v>
-      </c>
       <c r="AO3" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AP3" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>0.95</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU3" s="3" t="n">
         <v>46170.33333333334</v>
@@ -1361,64 +1361,64 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="O6" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P6" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="Q6" t="n">
         <v>4</v>
       </c>
       <c r="R6" t="n">
-        <v>1.89</v>
+        <v>1.85</v>
       </c>
       <c r="S6" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="T6" t="n">
-        <v>2.62</v>
+        <v>2.31</v>
       </c>
       <c r="U6" t="n">
         <v>3.25</v>
       </c>
       <c r="V6" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="W6" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE6" t="n">
         <v>1</v>
       </c>
-      <c r="X6" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AB6" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE6" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AF6" t="n">
-        <v>1.92</v>
+        <v>1.97</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="AJ6" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AK6" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="AL6" t="n">
         <v>0</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="O7" t="n">
-        <v>2.66</v>
+        <v>2.86</v>
       </c>
       <c r="P7" t="n">
-        <v>2.94</v>
+        <v>3.35</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R7" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="T7" t="n">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="U7" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="V7" t="n">
         <v>1.22</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>1.02</v>
       </c>
       <c r="X7" t="n">
         <v>1.07</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.52</v>
+        <v>1.49</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.36</v>
+        <v>2.45</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.9</v>
+        <v>4.65</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.56</v>
+        <v>1.67</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,7 +1590,7 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AK7" t="n">
         <v>1.51</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O8" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.75</v>
       </c>
-      <c r="O8" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="P8" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.08</v>
-      </c>
       <c r="U8" t="n">
-        <v>3.8</v>
+        <v>2.75</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="W8" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X8" t="n">
         <v>1.01</v>
       </c>
-      <c r="X8" t="n">
-        <v>1.14</v>
-      </c>
       <c r="Y8" t="n">
-        <v>1.56</v>
+        <v>1.26</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.63</v>
+        <v>1.98</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.38</v>
+        <v>1.83</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.54</v>
+        <v>3.14</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF8" t="n">
-        <v>2.1</v>
+        <v>1.71</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.65</v>
+        <v>1.95</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1749,10 +1749,10 @@
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1806,12 +1806,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1838,80 +1838,80 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>2</v>
+        <v>3.1</v>
       </c>
       <c r="R9" t="n">
-        <v>2.15</v>
+        <v>1.83</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.56</v>
       </c>
       <c r="T9" t="n">
-        <v>2.54</v>
+        <v>2.26</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>3.65</v>
       </c>
       <c r="V9" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.31</v>
       </c>
-      <c r="W9" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.25</v>
-      </c>
       <c r="AK9" t="n">
-        <v>2.3</v>
+        <v>1.51</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.3</v>
+        <v>2.75</v>
       </c>
       <c r="O10" t="n">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="P10" t="n">
-        <v>3.35</v>
+        <v>2.71</v>
       </c>
       <c r="Q10" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="S10" t="n">
-        <v>1.5</v>
+        <v>1.66</v>
       </c>
       <c r="T10" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="U10" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="V10" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W10" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
-        <v>1.07</v>
+        <v>1.14</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.49</v>
+        <v>1.56</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.45</v>
+        <v>1.38</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.65</v>
+        <v>5.54</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.51</v>
+        <v>1.4</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,12 +2124,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2156,65 +2156,65 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>3</v>
+        <v>1.6</v>
       </c>
       <c r="O11" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="P11" t="n">
-        <v>2.06</v>
+        <v>5.52</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.86</v>
+        <v>2.25</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="S11" t="n">
         <v>1.4</v>
       </c>
       <c r="T11" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="U11" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="V11" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W11" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>1.93</v>
+        <v>2.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.06</v>
+        <v>1.03</v>
       </c>
       <c r="AF11" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.71</v>
       </c>
-      <c r="AG11" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
           <t>[]</t>
@@ -2226,10 +2226,10 @@
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.31</v>
+        <v>1.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.31</v>
+        <v>2.12</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2273,22 +2273,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2315,64 +2315,64 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.45</v>
+        <v>2</v>
       </c>
       <c r="R12" t="n">
-        <v>1.97</v>
+        <v>2.15</v>
       </c>
       <c r="S12" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="U12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="V12" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="Z12" t="n">
         <v>2.88</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.86</v>
+        <v>3.7</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
@@ -2385,10 +2385,10 @@
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.79</v>
+        <v>2.3</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
@@ -2432,22 +2432,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2474,64 +2474,64 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.69</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P13" t="n">
         <v>3</v>
       </c>
-      <c r="P13" t="n">
-        <v>4.75</v>
-      </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
@@ -2591,22 +2591,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.4</v>
+        <v>1.69</v>
       </c>
       <c r="O14" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>2.55</v>
+        <v>4.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="V14" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.47</v>
+        <v>0</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
@@ -2792,64 +2792,64 @@
         </is>
       </c>
       <c r="N15" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
       <c r="O15" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.92</v>
+        <v>3.98</v>
       </c>
       <c r="R15" t="n">
-        <v>2.25</v>
+        <v>2.12</v>
       </c>
       <c r="S15" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="T15" t="n">
-        <v>2.7</v>
+        <v>2.53</v>
       </c>
       <c r="U15" t="n">
-        <v>2.74</v>
+        <v>3.02</v>
       </c>
       <c r="V15" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="W15" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>1.95</v>
+        <v>2.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.75</v>
+        <v>1.65</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.37</v>
+        <v>3.87</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="AE15" t="n">
-        <v>1.1</v>
+        <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
@@ -2862,10 +2862,10 @@
         </is>
       </c>
       <c r="AJ15" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AK15" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="AL15" t="n">
         <v>0</v>
@@ -3110,61 +3110,61 @@
         </is>
       </c>
       <c r="N17" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="O17" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="P17" t="n">
-        <v>3.68</v>
+        <v>3.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="R17" t="n">
-        <v>2.35</v>
+        <v>2.3</v>
       </c>
       <c r="S17" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>3.8</v>
+        <v>3.18</v>
       </c>
       <c r="U17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="W17" t="n">
-        <v>1.16</v>
+        <v>1.1</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.13</v>
+        <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.32</v>
+        <v>2.46</v>
       </c>
       <c r="AD17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AF17" t="n">
         <v>1.53</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="AF17" t="n">
-        <v>1.5</v>
       </c>
       <c r="AG17" t="n">
         <v>2.35</v>
@@ -3180,10 +3180,10 @@
         </is>
       </c>
       <c r="AJ17" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,16 +1011,16 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -1032,118 +1032,118 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.4</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>2.68</v>
+        <v>2.45</v>
       </c>
       <c r="P4" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="S4" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="U4" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W4" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF4" t="n">
         <v>2.25</v>
       </c>
-      <c r="Q4" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="R4" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="S4" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="T4" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="U4" t="n">
-        <v>4</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W4" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X4" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="Y4" t="n">
+      <c r="AG4" t="n">
         <v>1.57</v>
       </c>
-      <c r="Z4" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="AB4" t="n">
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
         <v>1.4</v>
       </c>
-      <c r="AC4" t="n">
-        <v>5.85</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AK4" t="n">
-        <v>1.22</v>
+        <v>1.53</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN4" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO4" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AP4" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>0.38</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46170.375</v>
@@ -1170,25 +1170,25 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
         <v>0</v>
@@ -1198,111 +1198,111 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N5" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="O5" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="P5" t="n">
         <v>2.2</v>
       </c>
-      <c r="O5" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="P5" t="n">
-        <v>3.15</v>
-      </c>
       <c r="Q5" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>2</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="T5" t="n">
-        <v>2.2</v>
+        <v>2.03</v>
       </c>
       <c r="U5" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.31</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.62</v>
+        <v>3.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.15</v>
+        <v>2.36</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '39']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.49</v>
+        <v>1.22</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO5" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AP5" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46170.375</v>
@@ -1338,26 +1338,26 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N6" t="n">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['24']</t>
         </is>
       </c>
       <c r="AJ6" t="n">
@@ -1440,28 +1440,28 @@
         <v>0</v>
       </c>
       <c r="AM6" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN6" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AO6" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP6" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AU6" s="3" t="n">
         <v>46170.41666666666</v>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1520,64 +1520,64 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.3</v>
+        <v>3.17</v>
       </c>
       <c r="O7" t="n">
-        <v>2.86</v>
+        <v>2.4</v>
       </c>
       <c r="P7" t="n">
-        <v>3.35</v>
+        <v>2.62</v>
       </c>
       <c r="Q7" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
       <c r="R7" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S7" t="n">
-        <v>1.5</v>
+        <v>1.73</v>
       </c>
       <c r="T7" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W7" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z7" t="n">
         <v>2.18</v>
       </c>
-      <c r="U7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.45</v>
-      </c>
       <c r="AA7" t="n">
-        <v>2.6</v>
+        <v>2.88</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.45</v>
+        <v>1.36</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.65</v>
+        <v>5.76</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
@@ -1590,10 +1590,10 @@
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
@@ -1637,22 +1637,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1679,80 +1679,80 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3.1</v>
+        <v>2.67</v>
       </c>
       <c r="P8" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2</v>
-      </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ8" t="n">
         <v>1.36</v>
       </c>
-      <c r="T8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U8" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF8" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ8" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK8" t="n">
-        <v>1.27</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="O9" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="P9" t="n">
-        <v>2.94</v>
+        <v>2.8</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R9" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="S9" t="n">
-        <v>1.56</v>
+        <v>1.51</v>
       </c>
       <c r="T9" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="U9" t="n">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.36</v>
+        <v>2.63</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.9</v>
+        <v>4.6</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.11</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>1.31</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.51</v>
+        <v>1.43</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1997,64 +1997,64 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.71</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="R10" t="n">
-        <v>1.9</v>
+        <v>2.15</v>
       </c>
       <c r="S10" t="n">
-        <v>1.66</v>
+        <v>1.44</v>
       </c>
       <c r="T10" t="n">
-        <v>2.08</v>
+        <v>2.53</v>
       </c>
       <c r="U10" t="n">
-        <v>3.8</v>
+        <v>3.1</v>
       </c>
       <c r="V10" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AD10" t="n">
         <v>1.2</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5.54</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.1</v>
-      </c>
       <c r="AE10" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.4</v>
+        <v>2.3</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2124,139 +2124,139 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N11" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="O11" t="n">
-        <v>3.45</v>
+        <v>3.1</v>
       </c>
       <c r="P11" t="n">
-        <v>5.52</v>
+        <v>2.2</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.25</v>
+        <v>3.88</v>
       </c>
       <c r="R11" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>2.67</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X11" t="n">
         <v>1.01</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.08</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.72</v>
+        <v>1.83</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.58</v>
+        <v>3.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.21</v>
+        <v>1.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AG11" t="n">
         <v>1.95</v>
       </c>
-      <c r="AG11" t="n">
-        <v>1.71</v>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '90+4']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '68', '76']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.12</v>
+        <v>1.27</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AO11" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP11" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46170.45833333334</v>
@@ -2273,32 +2273,32 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12" t="n">
         <v>0</v>
@@ -2311,29 +2311,29 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>5.52</v>
       </c>
       <c r="Q12" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="R12" t="n">
-        <v>2.15</v>
+        <v>2.04</v>
       </c>
       <c r="S12" t="n">
         <v>1.4</v>
       </c>
       <c r="T12" t="n">
-        <v>2.54</v>
+        <v>2.67</v>
       </c>
       <c r="U12" t="n">
         <v>3</v>
@@ -2342,80 +2342,80 @@
         <v>1.31</v>
       </c>
       <c r="W12" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AE12" t="n">
         <v>1.03</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF12" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
+          <t>['34']</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
       <c r="AJ12" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>2.3</v>
+        <v>2.12</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO12" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AS12" t="n">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46170.45833333334</v>
@@ -2633,64 +2633,64 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
         <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>4.75</v>
+        <v>4.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>3.68</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>2.61</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2703,10 +2703,10 @@
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,28 +1011,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1043,107 +1043,107 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>3.14</v>
       </c>
       <c r="O4" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="S4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="U4" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y4" t="n">
         <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.03</v>
+        <v>3.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.55</v>
+        <v>5.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
         <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '39']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP4" t="n">
         <v>6</v>
       </c>
-      <c r="AO4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.5</v>
+        <v>0.86</v>
       </c>
       <c r="AS4" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="AT4" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46170.375</v>
@@ -1170,28 +1170,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1202,107 +1202,107 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="S5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="T5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
         <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.17</v>
+        <v>3.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.9</v>
+        <v>5.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
         <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AG5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>['25', '39']</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.86</v>
-      </c>
       <c r="AS5" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46170.375</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,139 +1488,139 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>3.17</v>
+        <v>1.57</v>
       </c>
       <c r="O7" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="P7" t="n">
-        <v>2.62</v>
+        <v>5.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.5</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.87</v>
+        <v>2.15</v>
       </c>
       <c r="S7" t="n">
-        <v>1.73</v>
+        <v>1.44</v>
       </c>
       <c r="T7" t="n">
-        <v>1.99</v>
+        <v>2.53</v>
       </c>
       <c r="U7" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="V7" t="n">
-        <v>1.19</v>
+        <v>1.31</v>
       </c>
       <c r="W7" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="X7" t="n">
-        <v>1.16</v>
+        <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.59</v>
+        <v>1.36</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.18</v>
+        <v>2.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.88</v>
+        <v>2.2</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.36</v>
+        <v>1.62</v>
       </c>
       <c r="AC7" t="n">
-        <v>5.76</v>
+        <v>4.2</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.62</v>
+        <v>1.55</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['73', '90']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.36</v>
+        <v>2.3</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="AO7" t="n">
-        <v>-1</v>
+        <v>23</v>
       </c>
       <c r="AP7" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>0.71</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46170.45833333334</v>
@@ -1647,57 +1647,57 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="O8" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="P8" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R8" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="S8" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T8" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="U8" t="n">
         <v>3.4</v>
@@ -1706,37 +1706,37 @@
         <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X8" t="n">
         <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="AA8" t="n">
         <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF8" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1745,41 +1745,41 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+3', '81']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO8" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP8" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>0.93</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>0.39</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46170.45833333334</v>
@@ -1806,22 +1806,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -1830,33 +1830,33 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="O9" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="P9" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q9" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R9" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="S9" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="T9" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="U9" t="n">
         <v>3.4</v>
@@ -1865,80 +1865,80 @@
         <v>1.24</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
         <v>1.06</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="AA9" t="n">
         <v>2.5</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['80', '84']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AN9" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO9" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP9" t="n">
-        <v>-1</v>
+        <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>0.99</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46170.45833333334</v>
@@ -1955,149 +1955,149 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.1</v>
+        <v>3.88</v>
       </c>
       <c r="R10" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="S10" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="T10" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="U10" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="V10" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="W10" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="X10" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.2</v>
+        <v>1.98</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.62</v>
+        <v>1.83</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.2</v>
+        <v>3.14</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AF10" t="n">
-        <v>2.2</v>
+        <v>1.71</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '90+4']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['4', '68', '76']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.3</v>
+        <v>1.27</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN10" t="n">
-        <v>-1</v>
+        <v>12</v>
       </c>
       <c r="AO10" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AP10" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="AT10" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46170.45833333334</v>
@@ -2114,41 +2114,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>2</v>
       </c>
-      <c r="H11" t="n">
-        <v>3</v>
-      </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
         <v>1</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2156,107 +2156,107 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="O11" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="P11" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Q11" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="R11" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S11" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U11" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB11" t="n">
         <v>1.36</v>
       </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V11" t="n">
+      <c r="AC11" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>['20', '29']</t>
+        </is>
+      </c>
+      <c r="AJ11" t="n">
         <v>1.36</v>
       </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>['11', '90+4']</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>['4', '68', '76']</t>
-        </is>
-      </c>
-      <c r="AJ11" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK11" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN11" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AO11" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AP11" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.31</v>
+        <v>1.11</v>
       </c>
       <c r="AS11" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AT11" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46170.45833333334</v>
@@ -2451,26 +2451,26 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N13" t="n">
@@ -2535,12 +2535,12 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '64']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
@@ -2553,28 +2553,28 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="AN13" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO13" t="n">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>0.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="AT13" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46170.5</v>
@@ -2610,26 +2610,26 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N14" t="n">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['32', '60']</t>
         </is>
       </c>
       <c r="AJ14" t="n">
@@ -2712,28 +2712,28 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AN14" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AP14" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>0.74</v>
       </c>
       <c r="AS14" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="AT14" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46170.5</v>
@@ -2951,25 +2951,25 @@
         </is>
       </c>
       <c r="N16" t="n">
-        <v>1.5</v>
+        <v>1.39</v>
       </c>
       <c r="O16" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="P16" t="n">
-        <v>5</v>
+        <v>7.09</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.03</v>
+        <v>1.94</v>
       </c>
       <c r="R16" t="n">
-        <v>2.17</v>
+        <v>2.22</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="T16" t="n">
-        <v>3.2</v>
+        <v>2.97</v>
       </c>
       <c r="U16" t="n">
         <v>2.53</v>
@@ -2981,13 +2981,13 @@
         <v>1.09</v>
       </c>
       <c r="X16" t="n">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="Y16" t="n">
         <v>1.18</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.82</v>
+        <v>3.84</v>
       </c>
       <c r="AA16" t="n">
         <v>1.71</v>
@@ -2996,20 +2996,20 @@
         <v>2</v>
       </c>
       <c r="AC16" t="n">
-        <v>2.7</v>
+        <v>2.74</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AE16" t="n">
         <v>1.1</v>
       </c>
       <c r="AF16" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AG16" t="n">
         <v>1.81</v>
       </c>
-      <c r="AG16" t="n">
-        <v>1.86</v>
-      </c>
       <c r="AH16" t="inlineStr">
         <is>
           <t>[]</t>
@@ -3021,10 +3021,10 @@
         </is>
       </c>
       <c r="AJ16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.38</v>
+        <v>2.55</v>
       </c>
       <c r="AL16" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,28 +1011,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1043,107 +1043,107 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="P4" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q4" t="n">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="R4" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="S4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="T4" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="U4" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="V4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W4" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X4" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y4" t="n">
         <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.17</v>
+        <v>3.03</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.9</v>
+        <v>5.55</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
         <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AG4" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR4" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>['25', '39']</t>
-        </is>
-      </c>
-      <c r="AJ4" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.86</v>
-      </c>
       <c r="AS4" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="AT4" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46170.375</v>
@@ -1170,28 +1170,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1202,107 +1202,107 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>2.45</v>
+        <v>3.14</v>
       </c>
       <c r="O5" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="P5" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="R5" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="S5" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="U5" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="V5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W5" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X5" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y5" t="n">
         <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.03</v>
+        <v>3.17</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.55</v>
+        <v>5.9</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE5" t="n">
         <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '39']</t>
         </is>
       </c>
       <c r="AJ5" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK5" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AL5" t="n">
         <v>0</v>
       </c>
       <c r="AM5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN5" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP5" t="n">
         <v>6</v>
       </c>
-      <c r="AO5" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ5" t="n">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>1.5</v>
+        <v>0.86</v>
       </c>
       <c r="AS5" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="AT5" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46170.375</v>
@@ -1647,31 +1647,31 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="n">
         <v>2</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1679,25 +1679,25 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="P8" t="n">
-        <v>2.8</v>
+        <v>3.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="T8" t="n">
-        <v>2.31</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
         <v>3.4</v>
@@ -1706,53 +1706,53 @@
         <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.01</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
         <v>1.06</v>
       </c>
       <c r="Y8" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.63</v>
+        <v>2.57</v>
       </c>
       <c r="AA8" t="n">
         <v>2.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="AF8" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>['45+3', '81']</t>
+          <t>['80', '84']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
@@ -1761,25 +1761,25 @@
         <v>3</v>
       </c>
       <c r="AN8" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
         <v>9</v>
       </c>
       <c r="AP8" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.93</v>
+        <v>0.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.39</v>
+        <v>1.76</v>
       </c>
       <c r="AS8" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="AT8" t="n">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46170.45833333334</v>
@@ -1796,29 +1796,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
@@ -1830,7 +1830,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M9" t="inlineStr">
         <is>
@@ -1838,64 +1838,64 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>2.35</v>
+        <v>1.6</v>
       </c>
       <c r="O9" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P9" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S9" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T9" t="n">
         <v>2.67</v>
       </c>
-      <c r="P9" t="n">
+      <c r="U9" t="n">
+        <v>3</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z9" t="n">
         <v>3.15</v>
       </c>
-      <c r="Q9" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X9" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>2.57</v>
-      </c>
       <c r="AA9" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF9" t="n">
         <v>1.95</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
@@ -1904,41 +1904,41 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>['80', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="n">
         <v>3</v>
       </c>
-      <c r="AN9" t="n">
-        <v>6</v>
-      </c>
       <c r="AO9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AP9" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.99</v>
+        <v>1.32</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.76</v>
+        <v>0.93</v>
       </c>
       <c r="AS9" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="AT9" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46170.45833333334</v>
@@ -1955,41 +1955,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>2</v>
       </c>
-      <c r="H10" t="n">
-        <v>3</v>
-      </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1997,107 +1997,107 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.9</v>
+        <v>3.17</v>
       </c>
       <c r="O10" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="P10" t="n">
-        <v>2.2</v>
+        <v>2.62</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="R10" t="n">
-        <v>2</v>
+        <v>1.87</v>
       </c>
       <c r="S10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AB10" t="n">
         <v>1.36</v>
       </c>
-      <c r="T10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U10" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V10" t="n">
+      <c r="AC10" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>['70']</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>['20', '29']</t>
+        </is>
+      </c>
+      <c r="AJ10" t="n">
         <v>1.36</v>
       </c>
-      <c r="W10" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>['11', '90+4']</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>['4', '68', '76']</t>
-        </is>
-      </c>
-      <c r="AJ10" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AK10" t="n">
-        <v>1.27</v>
+        <v>1.36</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AN10" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="AO10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AP10" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.13</v>
+        <v>1.45</v>
       </c>
       <c r="AR10" t="n">
-        <v>2.31</v>
+        <v>1.11</v>
       </c>
       <c r="AS10" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AT10" t="n">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46170.45833333334</v>
@@ -2114,149 +2114,149 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H11" t="n">
+        <v>3</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
         <v>2</v>
       </c>
-      <c r="I11" t="n">
-        <v>0</v>
-      </c>
-      <c r="J11" t="n">
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N11" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="R11" t="n">
         <v>2</v>
       </c>
-      <c r="K11" t="n">
-        <v>1</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N11" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="O11" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.87</v>
-      </c>
       <c r="S11" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="T11" t="n">
-        <v>1.99</v>
+        <v>2.75</v>
       </c>
       <c r="U11" t="n">
-        <v>3.9</v>
+        <v>2.75</v>
       </c>
       <c r="V11" t="n">
-        <v>1.19</v>
+        <v>1.36</v>
       </c>
       <c r="W11" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X11" t="n">
         <v>1.01</v>
       </c>
-      <c r="X11" t="n">
-        <v>1.16</v>
-      </c>
       <c r="Y11" t="n">
-        <v>1.59</v>
+        <v>1.26</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.18</v>
+        <v>3.2</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.88</v>
+        <v>1.98</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.36</v>
+        <v>1.83</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.76</v>
+        <v>3.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.03</v>
+        <v>1.08</v>
       </c>
       <c r="AF11" t="n">
-        <v>2.15</v>
+        <v>1.71</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.62</v>
+        <v>1.95</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>['11', '90+4']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>['20', '29']</t>
+          <t>['4', '68', '76']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AO11" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AP11" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.45</v>
+        <v>1.13</v>
       </c>
       <c r="AR11" t="n">
-        <v>1.11</v>
+        <v>2.31</v>
       </c>
       <c r="AS11" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AT11" t="n">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46170.45833333334</v>
@@ -2273,41 +2273,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" t="inlineStr">
         <is>
@@ -2315,107 +2315,107 @@
         </is>
       </c>
       <c r="N12" t="n">
-        <v>1.6</v>
+        <v>2.44</v>
       </c>
       <c r="O12" t="n">
-        <v>3.45</v>
+        <v>2.65</v>
       </c>
       <c r="P12" t="n">
-        <v>5.52</v>
+        <v>2.8</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.25</v>
+        <v>3.3</v>
       </c>
       <c r="R12" t="n">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="S12" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="T12" t="n">
-        <v>2.67</v>
+        <v>2.31</v>
       </c>
       <c r="U12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>2</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>['45+3', '81']</t>
+        </is>
+      </c>
+      <c r="AJ12" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
         <v>3</v>
       </c>
-      <c r="V12" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>['34']</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AJ12" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>1</v>
-      </c>
       <c r="AN12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AP12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.32</v>
+        <v>0.93</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.93</v>
+        <v>0.39</v>
       </c>
       <c r="AS12" t="n">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="AT12" t="n">
-        <v>37</v>
+        <v>16</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46170.45833333334</v>
@@ -2432,32 +2432,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -2466,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2474,107 +2474,107 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="S13" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="U13" t="n">
-        <v>2.75</v>
+        <v>3.68</v>
       </c>
       <c r="V13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.4</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AC13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.04</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>['26', '64']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['32', '60']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AN13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AP13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="AS13" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="AT13" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46170.5</v>
@@ -2591,32 +2591,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2625,7 +2625,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2633,107 +2633,107 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" t="n">
-        <v>4.6</v>
-      </c>
       <c r="Q14" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="T14" t="n">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="U14" t="n">
-        <v>3.68</v>
+        <v>2.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.36</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.61</v>
+        <v>1.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.75</v>
+        <v>3.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['26', '64']</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>['32', '60']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AP14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="AT14" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46170.5</v>
@@ -2769,10 +2769,10 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
@@ -2781,63 +2781,63 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N15" t="n">
-        <v>2.9</v>
+        <v>2.93</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="P15" t="n">
-        <v>2.2</v>
+        <v>2.35</v>
       </c>
       <c r="Q15" t="n">
-        <v>3.98</v>
+        <v>3.78</v>
       </c>
       <c r="R15" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="S15" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="T15" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
       <c r="U15" t="n">
-        <v>3.02</v>
+        <v>2.96</v>
       </c>
       <c r="V15" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W15" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X15" t="n">
         <v>1.06</v>
       </c>
       <c r="Y15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="Z15" t="n">
         <v>3</v>
       </c>
       <c r="AA15" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AC15" t="n">
-        <v>3.87</v>
+        <v>3.77</v>
       </c>
       <c r="AD15" t="n">
         <v>1.22</v>
@@ -2846,19 +2846,19 @@
         <v>1.06</v>
       </c>
       <c r="AF15" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AG15" t="n">
         <v>1.85</v>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['78']</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['61']</t>
         </is>
       </c>
       <c r="AJ15" t="n">
@@ -2871,28 +2871,28 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AN15" t="n">
-        <v>-1</v>
+        <v>3</v>
       </c>
       <c r="AO15" t="n">
-        <v>-1</v>
+        <v>17</v>
       </c>
       <c r="AP15" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>2.29</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AS15" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="AT15" t="n">
-        <v>0</v>
+        <v>89</v>
       </c>
       <c r="AU15" s="3" t="n">
         <v>46170.52083333334</v>
@@ -2928,16 +2928,16 @@
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>0</v>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N16" t="n">
@@ -3012,12 +3012,12 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['15']</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['3', '20']</t>
         </is>
       </c>
       <c r="AJ16" t="n">
@@ -3030,28 +3030,28 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN16" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO16" t="n">
-        <v>-1</v>
+        <v>13</v>
       </c>
       <c r="AP16" t="n">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="AQ16" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AS16" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="AT16" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="AU16" s="3" t="n">
         <v>46170.54166666666</v>
@@ -3128,16 +3128,16 @@
         <v>1.28</v>
       </c>
       <c r="T17" t="n">
-        <v>3.18</v>
+        <v>3.5</v>
       </c>
       <c r="U17" t="n">
         <v>2.3</v>
       </c>
       <c r="V17" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="W17" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="X17" t="n">
         <v>1.03</v>
@@ -3146,22 +3146,22 @@
         <v>1.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="AB17" t="n">
-        <v>2.3</v>
+        <v>2.25</v>
       </c>
       <c r="AC17" t="n">
-        <v>2.46</v>
+        <v>2.41</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="AF17" t="n">
         <v>1.53</v>
@@ -3183,7 +3183,7 @@
         <v>1.22</v>
       </c>
       <c r="AK17" t="n">
-        <v>1.85</v>
+        <v>1.78</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1011,28 +1011,28 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Awassa Kenema</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ethiopia Bunna</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>1</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1043,107 +1043,107 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>3.14</v>
       </c>
       <c r="O4" t="n">
-        <v>2.45</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.12</v>
+        <v>4.2</v>
       </c>
       <c r="R4" t="n">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="S4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="T4" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="U4" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="V4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W4" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="X4" t="n">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="Y4" t="n">
         <v>1.6</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.21</v>
+        <v>2.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.03</v>
+        <v>3.17</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.55</v>
+        <v>5.9</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AE4" t="n">
         <v>1.01</v>
       </c>
       <c r="AF4" t="n">
-        <v>2.25</v>
+        <v>2.36</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>['61']</t>
+          <t>['29']</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['25', '39']</t>
         </is>
       </c>
       <c r="AJ4" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.53</v>
+        <v>1.22</v>
       </c>
       <c r="AL4" t="n">
         <v>0</v>
       </c>
       <c r="AM4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AN4" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP4" t="n">
         <v>6</v>
       </c>
-      <c r="AO4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>12</v>
-      </c>
       <c r="AQ4" t="n">
-        <v>0.38</v>
+        <v>0.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>1.5</v>
+        <v>0.86</v>
       </c>
       <c r="AS4" t="n">
-        <v>14</v>
+        <v>58</v>
       </c>
       <c r="AT4" t="n">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="AU4" s="3" t="n">
         <v>46170.375</v>
@@ -1170,28 +1170,28 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Awassa Kenema</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1202,107 +1202,107 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>3.14</v>
+        <v>2.45</v>
       </c>
       <c r="O5" t="n">
-        <v>2.8</v>
+        <v>2.45</v>
       </c>
       <c r="P5" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>4.2</v>
+        <v>3.12</v>
       </c>
       <c r="R5" t="n">
-        <v>1.72</v>
+        <v>1.93</v>
       </c>
       <c r="S5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="T5" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="V5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W5" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X5" t="n">
-        <v>1.13</v>
+        <v>1.1</v>
       </c>
       <c r="Y5" t="n">
         <v>1.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.1</v>
+        <v>2.21</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.17</v>
+        <v>3.03</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.9</v>
+        <v>5.55</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="AE5" t="n">
         <v>1.01</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AG5" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>['61']</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AJ5" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>2</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AR5" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>['29']</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>['25', '39']</t>
-        </is>
-      </c>
-      <c r="AJ5" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>3</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>4</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>6</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.86</v>
-      </c>
       <c r="AS5" t="n">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="AT5" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="AU5" s="3" t="n">
         <v>46170.375</v>
@@ -1478,7 +1478,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1488,20 +1488,20 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Septemvri Sofia</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Yantra 2019</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>2</v>
       </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
@@ -1509,10 +1509,10 @@
         <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -1520,107 +1520,107 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>1.57</v>
+        <v>2.44</v>
       </c>
       <c r="O7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="S7" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="U7" t="n">
         <v>3.4</v>
       </c>
-      <c r="P7" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="R7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="S7" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="T7" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="U7" t="n">
-        <v>3.1</v>
-      </c>
       <c r="V7" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="W7" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="X7" t="n">
         <v>1.06</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.36</v>
+        <v>1.48</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.8</v>
+        <v>2.63</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.62</v>
+        <v>1.48</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>['73', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>['42']</t>
+          <t>['45+3', '81']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.3</v>
+        <v>1.43</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AN7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AO7" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="AP7" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.05</v>
+        <v>0.93</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.71</v>
+        <v>0.39</v>
       </c>
       <c r="AS7" t="n">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="AT7" t="n">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46170.45833333334</v>
@@ -1637,29 +1637,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>2.35</v>
+        <v>1.6</v>
       </c>
       <c r="O8" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P8" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R8" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T8" t="n">
         <v>2.67</v>
       </c>
-      <c r="P8" t="n">
+      <c r="U8" t="n">
+        <v>3</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="Z8" t="n">
         <v>3.15</v>
       </c>
-      <c r="Q8" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="R8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="T8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="U8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1</v>
-      </c>
-      <c r="X8" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>2.57</v>
-      </c>
       <c r="AA8" t="n">
-        <v>2.5</v>
+        <v>2.08</v>
       </c>
       <c r="AB8" t="n">
-        <v>1.5</v>
+        <v>1.72</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.3</v>
+        <v>3.58</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="AE8" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AF8" t="n">
         <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1745,41 +1745,41 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>['80', '84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.36</v>
+        <v>1.22</v>
       </c>
       <c r="AK8" t="n">
-        <v>1.44</v>
+        <v>2.12</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="n">
         <v>3</v>
       </c>
-      <c r="AN8" t="n">
-        <v>6</v>
-      </c>
       <c r="AO8" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AP8" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.99</v>
+        <v>1.32</v>
       </c>
       <c r="AR8" t="n">
-        <v>1.76</v>
+        <v>0.93</v>
       </c>
       <c r="AS8" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="AT8" t="n">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46170.45833333334</v>
@@ -1796,38 +1796,38 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>Pharco</t>
         </is>
       </c>
       <c r="G9" t="n">
         <v>1</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -1838,107 +1838,107 @@
         </is>
       </c>
       <c r="N9" t="n">
-        <v>1.6</v>
+        <v>3.17</v>
       </c>
       <c r="O9" t="n">
-        <v>3.45</v>
+        <v>2.4</v>
       </c>
       <c r="P9" t="n">
-        <v>5.52</v>
+        <v>2.62</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="R9" t="n">
-        <v>2.04</v>
+        <v>1.87</v>
       </c>
       <c r="S9" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="T9" t="n">
-        <v>2.67</v>
+        <v>1.99</v>
       </c>
       <c r="U9" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="V9" t="n">
-        <v>1.31</v>
+        <v>1.19</v>
       </c>
       <c r="W9" t="n">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="X9" t="n">
-        <v>1.01</v>
+        <v>1.16</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.3</v>
+        <v>1.59</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.15</v>
+        <v>2.18</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.08</v>
+        <v>2.88</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.72</v>
+        <v>1.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.58</v>
+        <v>5.76</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.21</v>
+        <v>1.1</v>
       </c>
       <c r="AE9" t="n">
         <v>1.03</v>
       </c>
       <c r="AF9" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>['70']</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['20', '29']</t>
         </is>
       </c>
       <c r="AJ9" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.12</v>
+        <v>1.36</v>
       </c>
       <c r="AL9" t="n">
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AN9" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AO9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.32</v>
+        <v>1.45</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.93</v>
+        <v>1.11</v>
       </c>
       <c r="AS9" t="n">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="AT9" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="AU9" s="3" t="n">
         <v>46170.45833333334</v>
@@ -1965,12 +1965,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Pharco</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1980,124 +1980,124 @@
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="n">
         <v>2</v>
       </c>
-      <c r="K10" t="n">
-        <v>1</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N10" t="n">
-        <v>3.17</v>
+        <v>2.35</v>
       </c>
       <c r="O10" t="n">
-        <v>2.4</v>
+        <v>2.67</v>
       </c>
       <c r="P10" t="n">
-        <v>2.62</v>
+        <v>3.15</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="R10" t="n">
-        <v>1.87</v>
+        <v>2.1</v>
       </c>
       <c r="S10" t="n">
-        <v>1.73</v>
+        <v>1.48</v>
       </c>
       <c r="T10" t="n">
-        <v>1.99</v>
+        <v>2.2</v>
       </c>
       <c r="U10" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="V10" t="n">
-        <v>1.19</v>
+        <v>1.24</v>
       </c>
       <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE10" t="n">
         <v>1.01</v>
       </c>
-      <c r="X10" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>1.03</v>
-      </c>
       <c r="AF10" t="n">
-        <v>2.15</v>
+        <v>1.95</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.62</v>
+        <v>1.74</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>['70']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>['20', '29']</t>
+          <t>['80', '84']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
         <v>1.36</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AN10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO10" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AP10" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>1.45</v>
+        <v>0.99</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.11</v>
+        <v>1.76</v>
       </c>
       <c r="AS10" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="AT10" t="n">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46170.45833333334</v>
@@ -2114,41 +2114,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Septemvri Sofia</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>Yantra 2019</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
         <v>1</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M11" t="inlineStr">
         <is>
@@ -2156,80 +2156,80 @@
         </is>
       </c>
       <c r="N11" t="n">
-        <v>2.9</v>
+        <v>1.57</v>
       </c>
       <c r="O11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="P11" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="R11" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="S11" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="U11" t="n">
         <v>3.1</v>
       </c>
-      <c r="P11" t="n">
+      <c r="V11" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA11" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q11" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="R11" t="n">
-        <v>2</v>
-      </c>
-      <c r="S11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="X11" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>1.98</v>
-      </c>
       <c r="AB11" t="n">
-        <v>1.83</v>
+        <v>1.62</v>
       </c>
       <c r="AC11" t="n">
-        <v>3.14</v>
+        <v>4.2</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.27</v>
+        <v>1.2</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="AF11" t="n">
-        <v>1.71</v>
+        <v>2.2</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.95</v>
+        <v>1.55</v>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>['11', '90+4']</t>
+          <t>['73', '90']</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>['4', '68', '76']</t>
+          <t>['42']</t>
         </is>
       </c>
       <c r="AJ11" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AK11" t="n">
-        <v>1.27</v>
+        <v>2.3</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
@@ -2238,25 +2238,25 @@
         <v>4</v>
       </c>
       <c r="AN11" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="AO11" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="AQ11" t="n">
-        <v>1.13</v>
+        <v>2.05</v>
       </c>
       <c r="AR11" t="n">
-        <v>2.31</v>
+        <v>0.71</v>
       </c>
       <c r="AS11" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="AT11" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="AU11" s="3" t="n">
         <v>46170.45833333334</v>
@@ -2273,149 +2273,149 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L12" t="n">
         <v>2</v>
       </c>
-      <c r="I12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1</v>
-      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N12" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="O12" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="P12" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="R12" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S12" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="T12" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="U12" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="V12" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="W12" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X12" t="n">
         <v>1.01</v>
       </c>
-      <c r="X12" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y12" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AA12" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.6</v>
+        <v>3.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF12" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AG12" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '90+4']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>['45+3', '81']</t>
+          <t>['4', '68', '76']</t>
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AO12" t="n">
         <v>9</v>
       </c>
       <c r="AP12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.93</v>
+        <v>1.13</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.39</v>
+        <v>2.31</v>
       </c>
       <c r="AS12" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="AT12" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46170.45833333334</v>
@@ -2432,32 +2432,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -2466,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2474,107 +2474,107 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="O13" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P13" t="n">
         <v>3</v>
       </c>
-      <c r="P13" t="n">
-        <v>4.6</v>
-      </c>
       <c r="Q13" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="R13" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="S13" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="T13" t="n">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="U13" t="n">
-        <v>3.68</v>
+        <v>2.75</v>
       </c>
       <c r="V13" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="W13" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X13" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="Z13" t="n">
-        <v>2.36</v>
+        <v>2.97</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.61</v>
+        <v>1.99</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.75</v>
+        <v>3.28</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AE13" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF13" t="n">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['26', '64']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>['32', '60']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AN13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO13" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AP13" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="AT13" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46170.5</v>
@@ -2591,32 +2591,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
         <v>2</v>
       </c>
-      <c r="H14" t="n">
-        <v>1</v>
-      </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2625,7 +2625,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2633,107 +2633,107 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="O14" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="R14" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="S14" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="T14" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="U14" t="n">
-        <v>2.75</v>
+        <v>3.68</v>
       </c>
       <c r="V14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AB14" t="n">
         <v>1.4</v>
       </c>
-      <c r="W14" t="n">
+      <c r="AC14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE14" t="n">
         <v>1.04</v>
       </c>
-      <c r="X14" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE14" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF14" t="n">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>['26', '64']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['32', '60']</t>
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AN14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO14" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AP14" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="AS14" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="AT14" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46170.5</v>
@@ -3087,26 +3087,26 @@
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="N17" t="n">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['26', '38', '74']</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['31', '67']</t>
         </is>
       </c>
       <c r="AJ17" t="n">
@@ -3189,28 +3189,28 @@
         <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="AN17" t="n">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="AO17" t="n">
-        <v>-1</v>
+        <v>11</v>
       </c>
       <c r="AP17" t="n">
-        <v>-1</v>
+        <v>16</v>
       </c>
       <c r="AQ17" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="AT17" t="n">
-        <v>0</v>
+        <v>84</v>
       </c>
       <c r="AU17" s="3" t="n">
         <v>46170.64583333334</v>

--- a/jogos_2026-05-28.xlsx
+++ b/jogos_2026-05-28.xlsx
@@ -1478,149 +1478,149 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Yelimay Semey</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H7" t="n">
+        <v>3</v>
+      </c>
+      <c r="I7" t="n">
+        <v>1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>1</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1</v>
+      </c>
+      <c r="L7" t="n">
         <v>2</v>
       </c>
-      <c r="I7" t="n">
-        <v>0</v>
-      </c>
-      <c r="J7" t="n">
-        <v>1</v>
-      </c>
-      <c r="K7" t="n">
-        <v>0</v>
-      </c>
-      <c r="L7" t="n">
-        <v>1</v>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="O7" t="n">
-        <v>2.65</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>3.3</v>
+        <v>3.88</v>
       </c>
       <c r="R7" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="S7" t="n">
-        <v>1.51</v>
+        <v>1.36</v>
       </c>
       <c r="T7" t="n">
-        <v>2.31</v>
+        <v>2.75</v>
       </c>
       <c r="U7" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="V7" t="n">
-        <v>1.24</v>
+        <v>1.36</v>
       </c>
       <c r="W7" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="X7" t="n">
         <v>1.01</v>
       </c>
-      <c r="X7" t="n">
-        <v>1.06</v>
-      </c>
       <c r="Y7" t="n">
-        <v>1.48</v>
+        <v>1.26</v>
       </c>
       <c r="Z7" t="n">
-        <v>2.63</v>
+        <v>3.2</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.5</v>
+        <v>1.98</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.6</v>
+        <v>3.14</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.14</v>
+        <v>1.27</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="AF7" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.66</v>
+        <v>1.95</v>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['11', '90+4']</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>['45+3', '81']</t>
+          <t>['4', '68', '76']</t>
         </is>
       </c>
       <c r="AJ7" t="n">
-        <v>1.31</v>
+        <v>1.27</v>
       </c>
       <c r="AK7" t="n">
-        <v>1.43</v>
+        <v>1.27</v>
       </c>
       <c r="AL7" t="n">
         <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AN7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="AO7" t="n">
         <v>9</v>
       </c>
       <c r="AP7" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.93</v>
+        <v>1.13</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.39</v>
+        <v>2.31</v>
       </c>
       <c r="AS7" t="n">
-        <v>22</v>
+        <v>39</v>
       </c>
       <c r="AT7" t="n">
-        <v>16</v>
+        <v>56</v>
       </c>
       <c r="AU7" s="3" t="n">
         <v>46170.45833333334</v>
@@ -1637,29 +1637,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Petrojet</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>FC Caspiy</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G8" t="n">
         <v>1</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I8" t="n">
         <v>1</v>
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M8" t="inlineStr">
         <is>
@@ -1679,64 +1679,64 @@
         </is>
       </c>
       <c r="N8" t="n">
-        <v>1.6</v>
+        <v>2.35</v>
       </c>
       <c r="O8" t="n">
-        <v>3.45</v>
+        <v>2.67</v>
       </c>
       <c r="P8" t="n">
-        <v>5.52</v>
+        <v>3.15</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.25</v>
+        <v>3.2</v>
       </c>
       <c r="R8" t="n">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="S8" t="n">
-        <v>1.4</v>
+        <v>1.48</v>
       </c>
       <c r="T8" t="n">
-        <v>2.67</v>
+        <v>2.2</v>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="V8" t="n">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="W8" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AE8" t="n">
         <v>1.01</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AE8" t="n">
-        <v>1.03</v>
       </c>
       <c r="AF8" t="n">
         <v>1.95</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
@@ -1745,41 +1745,41 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['80', '84']</t>
         </is>
       </c>
       <c r="AJ8" t="n">
-        <v>1.22</v>
+        <v>1.36</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.12</v>
+        <v>1.44</v>
       </c>
       <c r="AL8" t="n">
         <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AN8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AO8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AP8" t="n">
         <v>14</v>
       </c>
-      <c r="AP8" t="n">
-        <v>7</v>
-      </c>
       <c r="AQ8" t="n">
-        <v>1.32</v>
+        <v>0.99</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.93</v>
+        <v>1.76</v>
       </c>
       <c r="AS8" t="n">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="AT8" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="AU8" s="3" t="n">
         <v>46170.45833333334</v>
@@ -1965,31 +1965,31 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Petrojet</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H10" t="n">
         <v>2</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10" t="n">
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M10" t="inlineStr">
         <is>
@@ -1997,25 +1997,25 @@
         </is>
       </c>
       <c r="N10" t="n">
-        <v>2.35</v>
+        <v>2.44</v>
       </c>
       <c r="O10" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="P10" t="n">
-        <v>3.15</v>
+        <v>2.8</v>
       </c>
       <c r="Q10" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R10" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="S10" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="T10" t="n">
-        <v>2.2</v>
+        <v>2.31</v>
       </c>
       <c r="U10" t="n">
         <v>3.4</v>
@@ -2024,53 +2024,53 @@
         <v>1.24</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>1.01</v>
       </c>
       <c r="X10" t="n">
         <v>1.06</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.57</v>
+        <v>2.63</v>
       </c>
       <c r="AA10" t="n">
         <v>2.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AF10" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>['34']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>['80', '84']</t>
+          <t>['45+3', '81']</t>
         </is>
       </c>
       <c r="AJ10" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="AK10" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
@@ -2079,25 +2079,25 @@
         <v>3</v>
       </c>
       <c r="AN10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AO10" t="n">
         <v>9</v>
       </c>
       <c r="AP10" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.99</v>
+        <v>0.93</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.76</v>
+        <v>0.39</v>
       </c>
       <c r="AS10" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="AT10" t="n">
-        <v>64</v>
+        <v>16</v>
       </c>
       <c r="AU10" s="3" t="n">
         <v>46170.45833333334</v>
@@ -2283,139 +2283,139 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yelimay Semey</t>
+          <t>FC Caspiy</t>
         </is>
       </c>
       <c r="G12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="N12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="O12" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="P12" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R12" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="T12" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="U12" t="n">
         <v>3</v>
       </c>
-      <c r="I12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L12" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="N12" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="O12" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="P12" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="R12" t="n">
-        <v>2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="U12" t="n">
-        <v>2.75</v>
-      </c>
       <c r="V12" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="W12" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X12" t="n">
         <v>1.01</v>
       </c>
       <c r="Y12" t="n">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>1.98</v>
+        <v>2.08</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.83</v>
+        <v>1.72</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.14</v>
+        <v>3.58</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.27</v>
+        <v>1.21</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.08</v>
+        <v>1.03</v>
       </c>
       <c r="AF12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AG12" t="n">
         <v>1.71</v>
       </c>
-      <c r="AG12" t="n">
-        <v>1.95</v>
-      </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>['11', '90+4']</t>
+          <t>['34']</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>['4', '68', '76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AJ12" t="n">
-        <v>1.27</v>
+        <v>1.22</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.27</v>
+        <v>2.12</v>
       </c>
       <c r="AL12" t="n">
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AN12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AO12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AP12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="AR12" t="n">
-        <v>2.31</v>
+        <v>0.93</v>
       </c>
       <c r="AS12" t="n">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="AT12" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="AU12" s="3" t="n">
         <v>46170.45833333334</v>
@@ -2432,32 +2432,32 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kairat</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>2</v>
       </c>
-      <c r="H13" t="n">
-        <v>1</v>
-      </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -2466,7 +2466,7 @@
         <v>1</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M13" t="inlineStr">
         <is>
@@ -2474,107 +2474,107 @@
         </is>
       </c>
       <c r="N13" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="O13" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="P13" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.7</v>
+        <v>2.51</v>
       </c>
       <c r="R13" t="n">
-        <v>2.1</v>
+        <v>1.85</v>
       </c>
       <c r="S13" t="n">
-        <v>1.44</v>
+        <v>1.55</v>
       </c>
       <c r="T13" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="U13" t="n">
-        <v>2.75</v>
+        <v>3.68</v>
       </c>
       <c r="V13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AB13" t="n">
         <v>1.4</v>
       </c>
-      <c r="W13" t="n">
+      <c r="AC13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AE13" t="n">
         <v>1.04</v>
       </c>
-      <c r="X13" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>2.97</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>3.28</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AE13" t="n">
-        <v>1.06</v>
-      </c>
       <c r="AF13" t="n">
-        <v>1.8</v>
+        <v>2.29</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.91</v>
+        <v>1.53</v>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>['26', '64']</t>
+          <t>['47']</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>['13']</t>
+          <t>['32', '60']</t>
         </is>
       </c>
       <c r="AJ13" t="n">
-        <v>1.34</v>
+        <v>1.28</v>
       </c>
       <c r="AK13" t="n">
-        <v>1.61</v>
+        <v>1.83</v>
       </c>
       <c r="AL13" t="n">
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="AN13" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO13" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AP13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AQ13" t="n">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="AR13" t="n">
-        <v>0.8</v>
+        <v>0.74</v>
       </c>
       <c r="AS13" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="AT13" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="AU13" s="3" t="n">
         <v>46170.5</v>
@@ -2591,32 +2591,32 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Mekelakeya</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>Kairat</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J14" t="n">
         <v>1</v>
@@ -2625,7 +2625,7 @@
         <v>1</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M14" t="inlineStr">
         <is>
@@ -2633,107 +2633,107 @@
         </is>
       </c>
       <c r="N14" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="O14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="P14" t="n">
         <v>3</v>
       </c>
-      <c r="P14" t="n">
-        <v>4.6</v>
-      </c>
       <c r="Q14" t="n">
-        <v>2.51</v>
+        <v>2.7</v>
       </c>
       <c r="R14" t="n">
-        <v>1.85</v>
+        <v>2.1</v>
       </c>
       <c r="S14" t="n">
-        <v>1.55</v>
+        <v>1.44</v>
       </c>
       <c r="T14" t="n">
-        <v>2.26</v>
+        <v>2.48</v>
       </c>
       <c r="U14" t="n">
-        <v>3.68</v>
+        <v>2.75</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="W14" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="X14" t="n">
-        <v>1.05</v>
+        <v>1.03</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.52</v>
+        <v>1.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.36</v>
+        <v>2.97</v>
       </c>
       <c r="AA14" t="n">
-        <v>2.61</v>
+        <v>1.99</v>
       </c>
       <c r="AB14" t="n">
-        <v>1.4</v>
+        <v>1.76</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.75</v>
+        <v>3.28</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.09</v>
+        <v>1.29</v>
       </c>
       <c r="AE14" t="n">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="AF14" t="n">
-        <v>2.29</v>
+        <v>1.8</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.53</v>
+        <v>1.91</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>['47']</t>
+          <t>['26', '64']</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>['32', '60']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AJ14" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.83</v>
+        <v>1.61</v>
       </c>
       <c r="AL14" t="n">
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="AN14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO14" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AP14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>1.01</v>
+        <v>1.45</v>
       </c>
       <c r="AR14" t="n">
-        <v>0.74</v>
+        <v>0.8</v>
       </c>
       <c r="AS14" t="n">
-        <v>56</v>
+        <v>37</v>
       </c>
       <c r="AT14" t="n">
-        <v>28</v>
+        <v>45</v>
       </c>
       <c r="AU14" s="3" t="n">
         <v>46170.5</v>
